--- a/2083_2084/estimate/budget maag estimate/Ward swasthya water tank/different size water tank.xlsx
+++ b/2083_2084/estimate/budget maag estimate/Ward swasthya water tank/different size water tank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\2083_2084\estimate\budget maag estimate\Ward swasthya water tank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F825A9E-A655-44F7-931A-1E77740C81DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6E881A-3B32-47F8-B3CB-F223C7A08773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'include dhara marmat'!$A$1:$K$173</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'With formula'!$A$1:$K$177</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'With formula'!$A$1:$K$182</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'include dhara marmat'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">WCR!$1:$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'With formula'!$1:$8</definedName>
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="174">
   <si>
     <t>S.N.</t>
   </si>
@@ -749,6 +749,12 @@
   </si>
   <si>
     <t>-as of item no. 11</t>
+  </si>
+  <si>
+    <t>-for kitchen setup at ward office</t>
+  </si>
+  <si>
+    <t>-at roof of ward office</t>
   </si>
 </sst>
 </file>
@@ -2936,29 +2942,75 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="64" fillId="0" borderId="19" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="64" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="64" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="64" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="64" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="64" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="64" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="64" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2976,24 +3028,6 @@
     <xf numFmtId="0" fontId="63" fillId="32" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3018,58 +3052,30 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="64" fillId="0" borderId="19" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="64" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="64" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="64" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="759">
     <cellStyle name="??" xfId="476" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4239,60 +4245,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
     </row>
     <row r="2" spans="1:10" ht="25.5">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="147" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="139"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="139"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="12"/>
@@ -4311,33 +4317,33 @@
         <v>52</v>
       </c>
       <c r="B6" s="6"/>
-      <c r="C6" s="140" t="e">
+      <c r="C6" s="149" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="141"/>
+      <c r="D6" s="150"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
         <v>53</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="140" t="e">
+      <c r="I6" s="149" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="141"/>
+      <c r="J6" s="150"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="151"/>
+      <c r="E7" s="151"/>
+      <c r="F7" s="151"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="152"/>
     </row>
     <row r="8" spans="1:10" ht="16.5">
       <c r="A8" t="s">
@@ -4364,32 +4370,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="133" t="s">
+      <c r="A10" s="153" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="133" t="s">
+      <c r="B10" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="135" t="s">
+      <c r="C10" s="155" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135" t="s">
+      <c r="D10" s="155"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="133" t="s">
+      <c r="G10" s="155"/>
+      <c r="H10" s="155"/>
+      <c r="I10" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="133" t="s">
+      <c r="J10" s="153" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="134"/>
-      <c r="B11" s="134"/>
+      <c r="A11" s="154"/>
+      <c r="B11" s="154"/>
       <c r="C11" s="14" t="s">
         <v>61</v>
       </c>
@@ -4408,8 +4414,8 @@
       <c r="H11" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
+      <c r="I11" s="154"/>
+      <c r="J11" s="154"/>
     </row>
     <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="22">
@@ -5336,12 +5342,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -5351,6 +5351,12 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5383,29 +5389,29 @@
       <c r="A1" s="38">
         <v>152</v>
       </c>
-      <c r="B1" s="142" t="s">
+      <c r="B1" s="156" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
     </row>
     <row r="2" spans="1:8" ht="15.75">
       <c r="A2" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="158" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
     </row>
     <row r="3" spans="1:8" ht="31.5">
       <c r="A3" s="40"/>
@@ -5433,7 +5439,7 @@
     </row>
     <row r="4" spans="1:8" ht="17.25">
       <c r="A4" s="40"/>
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="160" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="42" t="s">
@@ -5456,7 +5462,7 @@
     </row>
     <row r="5" spans="1:8" ht="17.25">
       <c r="A5" s="40"/>
-      <c r="B5" s="147"/>
+      <c r="B5" s="161"/>
       <c r="C5" s="47" t="s">
         <v>96</v>
       </c>
@@ -5480,7 +5486,7 @@
     </row>
     <row r="6" spans="1:8" ht="17.25">
       <c r="A6" s="40"/>
-      <c r="B6" s="148" t="s">
+      <c r="B6" s="162" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="44" t="s">
@@ -5504,7 +5510,7 @@
     </row>
     <row r="7" spans="1:8" ht="17.25">
       <c r="A7" s="40"/>
-      <c r="B7" s="149"/>
+      <c r="B7" s="163"/>
       <c r="C7" s="47" t="s">
         <v>100</v>
       </c>
@@ -5628,94 +5634,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="139" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="109"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
       <c r="L2" s="118"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="124"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
       <c r="L3" s="109"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="141"/>
+      <c r="K4" s="141"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="119" t="s">
         <v>139</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
       <c r="G6" s="61"/>
-      <c r="H6" s="123" t="s">
+      <c r="H6" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="123"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="144"/>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="3"/>
@@ -9064,10 +9070,10 @@
       <c r="B167" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="C167" s="130" t="s">
+      <c r="C167" s="137" t="s">
         <v>66</v>
       </c>
-      <c r="D167" s="130"/>
+      <c r="D167" s="137"/>
       <c r="E167" s="75" t="s">
         <v>67</v>
       </c>
@@ -9083,11 +9089,11 @@
       <c r="B168" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="C168" s="128">
+      <c r="C168" s="138">
         <f>+J165</f>
         <v>530004.91742540663</v>
       </c>
-      <c r="D168" s="128"/>
+      <c r="D168" s="138"/>
       <c r="E168" s="110"/>
       <c r="F168" s="108"/>
       <c r="G168" s="111"/>
@@ -9101,10 +9107,10 @@
       <c r="B169" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="C169" s="128">
+      <c r="C169" s="138">
         <v>480000</v>
       </c>
-      <c r="D169" s="128"/>
+      <c r="D169" s="138"/>
       <c r="E169" s="112">
         <v>100</v>
       </c>
@@ -9120,11 +9126,11 @@
       <c r="B170" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C170" s="128">
+      <c r="C170" s="138">
         <f>0.95*C169</f>
         <v>456000</v>
       </c>
-      <c r="D170" s="128"/>
+      <c r="D170" s="138"/>
       <c r="E170" s="113">
         <f>C170/C168*100</f>
         <v>86.036937584485301</v>
@@ -9141,11 +9147,11 @@
       <c r="B171" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="C171" s="128">
+      <c r="C171" s="138">
         <f>C168-C170</f>
         <v>74004.917425406631</v>
       </c>
-      <c r="D171" s="128"/>
+      <c r="D171" s="138"/>
       <c r="E171" s="113">
         <f>C171/C169*100</f>
         <v>15.417691130293049</v>
@@ -9162,11 +9168,11 @@
       <c r="B172" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C172" s="128">
+      <c r="C172" s="138">
         <f>E172*C169/100</f>
         <v>9600</v>
       </c>
-      <c r="D172" s="128"/>
+      <c r="D172" s="138"/>
       <c r="E172" s="113">
         <v>2</v>
       </c>
@@ -9182,11 +9188,11 @@
       <c r="B173" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C173" s="129">
+      <c r="C173" s="136">
         <f>E173*C169/100</f>
         <v>14400</v>
       </c>
-      <c r="D173" s="129"/>
+      <c r="D173" s="136"/>
       <c r="E173" s="113">
         <v>3</v>
       </c>
@@ -9202,6 +9208,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C172:D172"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -9209,13 +9222,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C172:D172"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9245,132 +9251,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="154" t="s">
+      <c r="B1" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="154" t="s">
+      <c r="C1" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="154" t="s">
+      <c r="D1" s="168" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="154" t="s">
+      <c r="E1" s="168" t="s">
         <v>166</v>
       </c>
-      <c r="F1" s="154" t="s">
+      <c r="F1" s="168" t="s">
         <v>164</v>
       </c>
-      <c r="G1" s="154" t="s">
+      <c r="G1" s="168" t="s">
         <v>165</v>
       </c>
-      <c r="H1" s="154" t="s">
+      <c r="H1" s="168" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="160" t="s">
+      <c r="I1" s="170" t="s">
         <v>162</v>
       </c>
       <c r="J1" s="164" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="156" t="s">
+      <c r="K1" s="167" t="s">
         <v>168</v>
       </c>
-      <c r="L1" s="156"/>
-      <c r="M1" s="153" t="s">
+      <c r="L1" s="167"/>
+      <c r="M1" s="165" t="s">
         <v>169</v>
       </c>
-      <c r="N1" s="153"/>
+      <c r="N1" s="165"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="155"/>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="161"/>
+      <c r="A2" s="169"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="164"/>
-      <c r="K2" s="162" t="s">
+      <c r="K2" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="157" t="s">
+      <c r="L2" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="150" t="s">
+      <c r="M2" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="150" t="s">
+      <c r="N2" s="122" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="151">
+      <c r="A3" s="123">
         <f>14.5/3.281</f>
         <v>4.4193843340444987</v>
       </c>
-      <c r="B3" s="151">
+      <c r="B3" s="123">
         <f>14/3.281</f>
         <v>4.2669917708015843</v>
       </c>
-      <c r="C3" s="151">
+      <c r="C3" s="123">
         <f>5.5/3.281</f>
         <v>1.6763181956720512</v>
       </c>
-      <c r="D3" s="151">
+      <c r="D3" s="123">
         <v>0.125</v>
       </c>
-      <c r="E3" s="151">
+      <c r="E3" s="123">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F3" s="151">
+      <c r="F3" s="123">
         <f>8/12/3.281</f>
         <v>0.20319008432388497</v>
       </c>
-      <c r="G3" s="151">
+      <c r="G3" s="123">
         <f>1.5/12/3.281</f>
         <v>3.8098140810728431E-2</v>
       </c>
-      <c r="H3" s="151">
+      <c r="H3" s="123">
         <v>0.05</v>
       </c>
-      <c r="I3" s="158">
+      <c r="I3" s="126">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J3" s="152">
+      <c r="J3" s="124">
         <v>8</v>
       </c>
-      <c r="K3" s="163">
+      <c r="K3" s="128">
         <f>2/3.281</f>
         <v>0.6095702529716549</v>
       </c>
-      <c r="L3" s="158">
+      <c r="L3" s="126">
         <f>2/3.281</f>
         <v>0.6095702529716549</v>
       </c>
-      <c r="M3" s="151">
+      <c r="M3" s="123">
         <f>1/3.281</f>
         <v>0.30478512648582745</v>
       </c>
-      <c r="N3" s="151">
+      <c r="N3" s="123">
         <f>1/3.281</f>
         <v>0.30478512648582745</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="J4" s="152">
+      <c r="J4" s="124">
         <f>57*J3/1000</f>
         <v>0.45600000000000002</v>
       </c>
-      <c r="M4" s="159">
+      <c r="M4" s="166">
         <f>SQRT(('Size of water tank'!M3)^2+('Size of water tank'!N3)^2)</f>
         <v>0.43103125948585641</v>
       </c>
-      <c r="N4" s="159"/>
+      <c r="N4" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -9395,7 +9401,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07E67D-5D7A-4E99-87D9-10A521F06797}">
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="69" customWidth="1"/>
@@ -9413,94 +9419,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="139" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="109"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
       <c r="L2" s="118"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="124"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
       <c r="L3" s="109"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="141"/>
+      <c r="K4" s="141"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="119" t="s">
         <v>139</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="127"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
       <c r="G6" s="61"/>
-      <c r="H6" s="123" t="s">
+      <c r="H6" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="123"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="144"/>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="3"/>
@@ -10437,44 +10443,53 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="77"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="84"/>
+      <c r="B49" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="C49" s="83">
+        <f>TRUNC((D50-0.1)/0.15,0)+1</f>
+        <v>4</v>
+      </c>
+      <c r="D49" s="84">
+        <v>1.5</v>
+      </c>
       <c r="E49" s="84"/>
-      <c r="F49" s="84"/>
+      <c r="F49" s="84">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
       <c r="G49" s="84">
-        <f>SUM(G36:G48)</f>
-        <v>1016.9746824788764</v>
-      </c>
-      <c r="H49" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="84">
-        <f>132360/1000</f>
-        <v>132.36000000000001</v>
-      </c>
-      <c r="J49" s="95">
-        <f>G49*I49</f>
-        <v>134606.7689729041</v>
-      </c>
+        <f>C49*D49*F49</f>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="H49" s="80"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
       <c r="K49" s="81"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="77"/>
-      <c r="B50" s="92" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="84"/>
+      <c r="B50" s="94"/>
+      <c r="C50" s="83">
+        <f>TRUNC(D49/0.15,0)+1</f>
+        <v>11</v>
+      </c>
+      <c r="D50" s="84">
+        <f>2.25/3.281</f>
+        <v>0.68576653459311188</v>
+      </c>
       <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="84"/>
+      <c r="F50" s="84">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="G50" s="84">
+        <f>C50*D50*F50</f>
+        <v>6.7052727826882048</v>
+      </c>
       <c r="H50" s="80"/>
       <c r="I50" s="84"/>
-      <c r="J50" s="84">
-        <f>0.13*G49*106200/1000</f>
-        <v>14040.352466303368</v>
-      </c>
+      <c r="J50" s="84"/>
       <c r="K50" s="81"/>
     </row>
     <row r="51" spans="1:11">
@@ -10484,18 +10499,27 @@
       <c r="D51" s="84"/>
       <c r="E51" s="84"/>
       <c r="F51" s="84"/>
-      <c r="G51" s="84"/>
-      <c r="H51" s="80"/>
-      <c r="I51" s="84"/>
-      <c r="J51" s="84"/>
+      <c r="G51" s="84">
+        <f>SUM(G36:G50)</f>
+        <v>1029.0132885948979</v>
+      </c>
+      <c r="H51" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="84">
+        <f>132360/1000</f>
+        <v>132.36000000000001</v>
+      </c>
+      <c r="J51" s="95">
+        <f>G51*I51</f>
+        <v>136200.19887842069</v>
+      </c>
       <c r="K51" s="81"/>
     </row>
-    <row r="52" spans="1:11" ht="30.75">
-      <c r="A52" s="77">
-        <v>7</v>
-      </c>
-      <c r="B52" s="115" t="s">
-        <v>112</v>
+    <row r="52" spans="1:11">
+      <c r="A52" s="77"/>
+      <c r="B52" s="92" t="s">
+        <v>72</v>
       </c>
       <c r="C52" s="83"/>
       <c r="D52" s="84"/>
@@ -10504,54 +10528,37 @@
       <c r="G52" s="84"/>
       <c r="H52" s="80"/>
       <c r="I52" s="84"/>
-      <c r="J52" s="84"/>
+      <c r="J52" s="84">
+        <f>0.13*G51*106200/1000</f>
+        <v>14206.557462341161</v>
+      </c>
       <c r="K52" s="81"/>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="77"/>
-      <c r="B53" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="83">
-        <v>1</v>
-      </c>
-      <c r="D53" s="84">
-        <f>('Size of water tank'!A3+'Size of water tank'!B3)*2</f>
-        <v>17.372752209692166</v>
-      </c>
+      <c r="B53" s="92"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="84"/>
       <c r="E53" s="84"/>
-      <c r="F53" s="84">
-        <f>'Size of water tank'!C3+'Size of water tank'!D3</f>
-        <v>1.8013181956720512</v>
-      </c>
-      <c r="G53" s="84">
-        <f>PRODUCT(C53:F53)</f>
-        <v>31.293854664220333</v>
-      </c>
+      <c r="F53" s="84"/>
+      <c r="G53" s="84"/>
       <c r="H53" s="80"/>
       <c r="I53" s="84"/>
       <c r="J53" s="84"/>
       <c r="K53" s="81"/>
     </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="77"/>
-      <c r="B54" s="92"/>
-      <c r="C54" s="83">
-        <v>1</v>
-      </c>
-      <c r="D54" s="84">
-        <f>(('Size of water tank'!A3-'Size of water tank'!F3*2)+('Size of water tank'!B3-'Size of water tank'!F3*2))*2</f>
-        <v>15.747231535101086</v>
-      </c>
+    <row r="54" spans="1:11" ht="30.75">
+      <c r="A54" s="77">
+        <v>7</v>
+      </c>
+      <c r="B54" s="115" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="83"/>
+      <c r="D54" s="84"/>
       <c r="E54" s="84"/>
-      <c r="F54" s="84">
-        <f>'Size of water tank'!C3+'Size of water tank'!D3-'Size of water tank'!N3</f>
-        <v>1.4965330691862238</v>
-      </c>
-      <c r="G54" s="84">
-        <f t="shared" ref="G54:G56" si="7">PRODUCT(C54:F54)</f>
-        <v>23.566252740410917</v>
-      </c>
+      <c r="F54" s="84"/>
+      <c r="G54" s="84"/>
       <c r="H54" s="80"/>
       <c r="I54" s="84"/>
       <c r="J54" s="84"/>
@@ -10560,23 +10567,23 @@
     <row r="55" spans="1:11">
       <c r="A55" s="77"/>
       <c r="B55" s="94" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C55" s="83">
         <v>1</v>
       </c>
-      <c r="D55" s="165">
-        <f>'Size of water tank'!A3-'Size of water tank'!F3*2</f>
-        <v>4.0130041653967288</v>
-      </c>
-      <c r="E55" s="165">
-        <f>'Size of water tank'!B3-'Size of water tank'!F3*2</f>
-        <v>3.8606116021538144</v>
-      </c>
-      <c r="F55" s="84"/>
+      <c r="D55" s="84">
+        <f>('Size of water tank'!A3+'Size of water tank'!B3)*2</f>
+        <v>17.372752209692166</v>
+      </c>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84">
+        <f>'Size of water tank'!C3+'Size of water tank'!D3</f>
+        <v>1.8013181956720512</v>
+      </c>
       <c r="G55" s="84">
-        <f t="shared" si="7"/>
-        <v>15.492650440422196</v>
+        <f>PRODUCT(C55:F55)</f>
+        <v>31.293854664220333</v>
       </c>
       <c r="H55" s="80"/>
       <c r="I55" s="84"/>
@@ -10585,24 +10592,22 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="77"/>
-      <c r="B56" s="94" t="s">
-        <v>122</v>
-      </c>
+      <c r="B56" s="92"/>
       <c r="C56" s="83">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D56" s="84">
-        <f>'Size of water tank'!K3</f>
-        <v>0.6095702529716549</v>
-      </c>
-      <c r="E56" s="84">
-        <f>'Size of water tank'!L3</f>
-        <v>0.6095702529716549</v>
-      </c>
-      <c r="F56" s="84"/>
+        <f>(('Size of water tank'!A3-'Size of water tank'!F3*2)+('Size of water tank'!B3-'Size of water tank'!F3*2))*2</f>
+        <v>15.747231535101086</v>
+      </c>
+      <c r="E56" s="84"/>
+      <c r="F56" s="84">
+        <f>'Size of water tank'!C3+'Size of water tank'!D3-'Size of water tank'!N3</f>
+        <v>1.4965330691862238</v>
+      </c>
       <c r="G56" s="84">
-        <f t="shared" si="7"/>
-        <v>-0.37157589330792734</v>
+        <f t="shared" ref="G56:G59" si="7">PRODUCT(C56:F56)</f>
+        <v>23.566252740410917</v>
       </c>
       <c r="H56" s="80"/>
       <c r="I56" s="84"/>
@@ -10611,155 +10616,149 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="77"/>
-      <c r="B57" s="92"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="84"/>
-      <c r="E57" s="84"/>
+      <c r="B57" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="83">
+        <v>1</v>
+      </c>
+      <c r="D57" s="129">
+        <f>'Size of water tank'!A3-'Size of water tank'!F3*2</f>
+        <v>4.0130041653967288</v>
+      </c>
+      <c r="E57" s="129">
+        <f>'Size of water tank'!B3-'Size of water tank'!F3*2</f>
+        <v>3.8606116021538144</v>
+      </c>
       <c r="F57" s="84"/>
       <c r="G57" s="84">
-        <f>SUM(G53:G56)</f>
-        <v>69.981181951745512</v>
-      </c>
-      <c r="H57" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="I57" s="84">
-        <v>922.71</v>
-      </c>
-      <c r="J57" s="84">
-        <f>G57*I57</f>
-        <v>64572.336398695101</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>15.492650440422196</v>
+      </c>
+      <c r="H57" s="80"/>
+      <c r="I57" s="84"/>
+      <c r="J57" s="84"/>
       <c r="K57" s="81"/>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="77"/>
-      <c r="B58" s="92" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" s="83"/>
-      <c r="D58" s="84"/>
-      <c r="E58" s="84"/>
+      <c r="B58" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="83">
+        <v>-1</v>
+      </c>
+      <c r="D58" s="84">
+        <f>'Size of water tank'!K3</f>
+        <v>0.6095702529716549</v>
+      </c>
+      <c r="E58" s="84">
+        <f>'Size of water tank'!L3</f>
+        <v>0.6095702529716549</v>
+      </c>
       <c r="F58" s="84"/>
-      <c r="G58" s="84"/>
+      <c r="G58" s="84">
+        <f t="shared" si="7"/>
+        <v>-0.37157589330792734</v>
+      </c>
       <c r="H58" s="80"/>
       <c r="I58" s="84"/>
-      <c r="J58" s="84">
-        <f>0.13*G57*46827.87/100</f>
-        <v>4260.1905981474911</v>
-      </c>
+      <c r="J58" s="84"/>
       <c r="K58" s="81"/>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="77"/>
-      <c r="B59" s="92"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="84"/>
-      <c r="E59" s="84"/>
+      <c r="B59" s="94" t="str">
+        <f>B49</f>
+        <v>-for kitchen setup at ward office</v>
+      </c>
+      <c r="C59" s="83">
+        <v>1</v>
+      </c>
+      <c r="D59" s="84">
+        <f>D49</f>
+        <v>1.5</v>
+      </c>
+      <c r="E59" s="84">
+        <f>D50</f>
+        <v>0.68576653459311188</v>
+      </c>
       <c r="F59" s="84"/>
-      <c r="G59" s="84"/>
+      <c r="G59" s="84">
+        <f t="shared" si="7"/>
+        <v>1.0286498018896677</v>
+      </c>
       <c r="H59" s="80"/>
       <c r="I59" s="84"/>
       <c r="J59" s="84"/>
       <c r="K59" s="81"/>
     </row>
-    <row r="60" spans="1:11" ht="30.75">
-      <c r="A60" s="77">
-        <v>8</v>
-      </c>
-      <c r="B60" s="115" t="s">
-        <v>119</v>
-      </c>
+    <row r="60" spans="1:11">
+      <c r="A60" s="77"/>
+      <c r="B60" s="92"/>
       <c r="C60" s="83"/>
       <c r="D60" s="84"/>
       <c r="E60" s="84"/>
       <c r="F60" s="84"/>
-      <c r="G60" s="84"/>
-      <c r="H60" s="80"/>
-      <c r="I60" s="84"/>
-      <c r="J60" s="84"/>
+      <c r="G60" s="84">
+        <f>SUM(G55:G59)</f>
+        <v>71.009831753635183</v>
+      </c>
+      <c r="H60" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="84">
+        <v>922.71</v>
+      </c>
+      <c r="J60" s="84">
+        <f>G60*I60</f>
+        <v>65521.48185739672</v>
+      </c>
       <c r="K60" s="81"/>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="77"/>
-      <c r="B61" s="94" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="83">
-        <v>2</v>
-      </c>
-      <c r="D61" s="84">
-        <f>'Size of water tank'!A3</f>
-        <v>4.4193843340444987</v>
-      </c>
-      <c r="E61" s="84">
-        <f>'Size of water tank'!B3</f>
-        <v>4.2669917708015843</v>
-      </c>
-      <c r="F61" s="84">
-        <f>'Size of water tank'!D3</f>
-        <v>0.125</v>
-      </c>
-      <c r="G61" s="84">
-        <f>C61*D61*E61*F61</f>
-        <v>4.7143691463443291</v>
-      </c>
+      <c r="B61" s="92" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" s="83"/>
+      <c r="D61" s="84"/>
+      <c r="E61" s="84"/>
+      <c r="F61" s="84"/>
+      <c r="G61" s="84"/>
       <c r="H61" s="80"/>
       <c r="I61" s="84"/>
-      <c r="J61" s="84"/>
+      <c r="J61" s="84">
+        <f>0.13*G60*46827.87/100</f>
+        <v>4322.8109211054307</v>
+      </c>
       <c r="K61" s="81"/>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="77"/>
-      <c r="B62" s="94" t="s">
-        <v>116</v>
-      </c>
-      <c r="C62" s="83">
-        <v>2</v>
-      </c>
-      <c r="D62" s="84">
-        <f>'Size of water tank'!A3</f>
-        <v>4.4193843340444987</v>
-      </c>
-      <c r="E62" s="84">
-        <f>'Size of water tank'!F3</f>
-        <v>0.20319008432388497</v>
-      </c>
-      <c r="F62" s="84">
-        <f>'Size of water tank'!C3</f>
-        <v>1.6763181956720512</v>
-      </c>
-      <c r="G62" s="84">
-        <f>C62*D62*E62*F62</f>
-        <v>3.0105839166216812</v>
-      </c>
+      <c r="B62" s="92"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="84"/>
+      <c r="E62" s="84"/>
+      <c r="F62" s="84"/>
+      <c r="G62" s="84"/>
       <c r="H62" s="80"/>
       <c r="I62" s="84"/>
       <c r="J62" s="84"/>
       <c r="K62" s="81"/>
     </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="77"/>
-      <c r="B63" s="93"/>
-      <c r="C63" s="83">
-        <v>2</v>
-      </c>
-      <c r="D63" s="84">
-        <f>'Size of water tank'!B3-'Size of water tank'!F3*2</f>
-        <v>3.8606116021538144</v>
-      </c>
-      <c r="E63" s="84">
-        <f>'Size of water tank'!F3</f>
-        <v>0.20319008432388497</v>
-      </c>
-      <c r="F63" s="84">
-        <f>'Size of water tank'!C3</f>
-        <v>1.6763181956720512</v>
-      </c>
-      <c r="G63" s="84">
-        <f>C63*D63*E63*F63</f>
-        <v>2.6299353754396293</v>
-      </c>
+    <row r="63" spans="1:11" ht="30.75">
+      <c r="A63" s="77">
+        <v>8</v>
+      </c>
+      <c r="B63" s="115" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="83"/>
+      <c r="D63" s="84"/>
+      <c r="E63" s="84"/>
+      <c r="F63" s="84"/>
+      <c r="G63" s="84"/>
       <c r="H63" s="80"/>
       <c r="I63" s="84"/>
       <c r="J63" s="84"/>
@@ -10768,27 +10767,26 @@
     <row r="64" spans="1:11">
       <c r="A64" s="77"/>
       <c r="B64" s="94" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C64" s="83">
-        <f>2*0.5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="84">
-        <f>(('Size of water tank'!A3-('Size of water tank'!F3)*2)+('Size of water tank'!A3-('Size of water tank'!F3)*2-('Size of water tank'!M3)*2))/2</f>
-        <v>3.7082190389109013</v>
+        <f>'Size of water tank'!A3</f>
+        <v>4.4193843340444987</v>
       </c>
       <c r="E64" s="84">
-        <f>'Size of water tank'!M3</f>
-        <v>0.30478512648582745</v>
+        <f>'Size of water tank'!B3</f>
+        <v>4.2669917708015843</v>
       </c>
       <c r="F64" s="84">
-        <f>'Size of water tank'!N3</f>
-        <v>0.30478512648582745</v>
+        <f>'Size of water tank'!D3</f>
+        <v>0.125</v>
       </c>
       <c r="G64" s="84">
-        <f>C64*D64*E64*F64</f>
-        <v>0.34447120049119545</v>
+        <f t="shared" ref="G64:G70" si="8">C64*D64*E64*F64</f>
+        <v>4.7143691463443291</v>
       </c>
       <c r="H64" s="80"/>
       <c r="I64" s="84"/>
@@ -10797,26 +10795,27 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="77"/>
-      <c r="B65" s="94"/>
+      <c r="B65" s="94" t="s">
+        <v>116</v>
+      </c>
       <c r="C65" s="83">
-        <f>2*0.5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="84">
-        <f>(('Size of water tank'!B3-'Size of water tank'!F3*2)+('Size of water tank'!B3-'Size of water tank'!F3*2-'Size of water tank'!M3*2))/2</f>
-        <v>3.5558264756679869</v>
+        <f>'Size of water tank'!A3</f>
+        <v>4.4193843340444987</v>
       </c>
       <c r="E65" s="84">
-        <f>'Size of water tank'!M3</f>
-        <v>0.30478512648582745</v>
+        <f>'Size of water tank'!F3</f>
+        <v>0.20319008432388497</v>
       </c>
       <c r="F65" s="84">
-        <f>'Size of water tank'!N3</f>
-        <v>0.30478512648582745</v>
+        <f>'Size of water tank'!C3</f>
+        <v>1.6763181956720512</v>
       </c>
       <c r="G65" s="84">
-        <f>C65*D65*E65*F65</f>
-        <v>0.33031484978607778</v>
+        <f t="shared" si="8"/>
+        <v>3.0105839166216812</v>
       </c>
       <c r="H65" s="80"/>
       <c r="I65" s="84"/>
@@ -10825,25 +10824,25 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="77"/>
-      <c r="B66" s="94" t="s">
-        <v>122</v>
-      </c>
+      <c r="B66" s="93"/>
       <c r="C66" s="83">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D66" s="84">
-        <v>0.6</v>
+        <f>'Size of water tank'!B3-'Size of water tank'!F3*2</f>
+        <v>3.8606116021538144</v>
       </c>
       <c r="E66" s="84">
-        <v>0.6</v>
+        <f>'Size of water tank'!F3</f>
+        <v>0.20319008432388497</v>
       </c>
       <c r="F66" s="84">
-        <f>0.42/3.281</f>
-        <v>0.12800975312404753</v>
+        <f>'Size of water tank'!C3</f>
+        <v>1.6763181956720512</v>
       </c>
       <c r="G66" s="84">
-        <f>C66*D66*E66*F66</f>
-        <v>-4.6083511124657105E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.6299353754396293</v>
       </c>
       <c r="H66" s="80"/>
       <c r="I66" s="84"/>
@@ -10852,105 +10851,147 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="77"/>
-      <c r="B67" s="94"/>
-      <c r="C67" s="83"/>
-      <c r="D67" s="84"/>
-      <c r="E67" s="84" t="s">
-        <v>31</v>
-      </c>
-      <c r="F67" s="84"/>
+      <c r="B67" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="83">
+        <f>2*0.5</f>
+        <v>1</v>
+      </c>
+      <c r="D67" s="84">
+        <f>(('Size of water tank'!A3-('Size of water tank'!F3)*2)+('Size of water tank'!A3-('Size of water tank'!F3)*2-('Size of water tank'!M3)*2))/2</f>
+        <v>3.7082190389109013</v>
+      </c>
+      <c r="E67" s="84">
+        <f>'Size of water tank'!M3</f>
+        <v>0.30478512648582745</v>
+      </c>
+      <c r="F67" s="84">
+        <f>'Size of water tank'!N3</f>
+        <v>0.30478512648582745</v>
+      </c>
       <c r="G67" s="84">
-        <f>SUM(G61:G66)</f>
-        <v>10.983590977558256</v>
-      </c>
-      <c r="H67" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="I67" s="84">
-        <v>13957.29</v>
-      </c>
-      <c r="J67" s="95">
-        <f>G67*I67</f>
-        <v>153301.16451516407</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>0.34447120049119545</v>
+      </c>
+      <c r="H67" s="80"/>
+      <c r="I67" s="84"/>
+      <c r="J67" s="84"/>
       <c r="K67" s="81"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="77"/>
-      <c r="B68" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="C68" s="83"/>
-      <c r="D68" s="84"/>
-      <c r="E68" s="84"/>
-      <c r="F68" s="84"/>
-      <c r="G68" s="84"/>
+      <c r="B68" s="94"/>
+      <c r="C68" s="83">
+        <f>2*0.5</f>
+        <v>1</v>
+      </c>
+      <c r="D68" s="84">
+        <f>(('Size of water tank'!B3-'Size of water tank'!F3*2)+('Size of water tank'!B3-'Size of water tank'!F3*2-'Size of water tank'!M3*2))/2</f>
+        <v>3.5558264756679869</v>
+      </c>
+      <c r="E68" s="84">
+        <f>'Size of water tank'!M3</f>
+        <v>0.30478512648582745</v>
+      </c>
+      <c r="F68" s="84">
+        <f>'Size of water tank'!N3</f>
+        <v>0.30478512648582745</v>
+      </c>
+      <c r="G68" s="84">
+        <f t="shared" si="8"/>
+        <v>0.33031484978607778</v>
+      </c>
       <c r="H68" s="80"/>
       <c r="I68" s="84"/>
-      <c r="J68" s="84">
-        <f>0.13*G67*5212.4</f>
-        <v>7442.613049485205</v>
-      </c>
+      <c r="J68" s="84"/>
       <c r="K68" s="81"/>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="77"/>
-      <c r="B69" s="92" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="83"/>
-      <c r="D69" s="84"/>
-      <c r="E69" s="84"/>
-      <c r="F69" s="84"/>
-      <c r="G69" s="84"/>
+      <c r="B69" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="C69" s="83">
+        <v>-1</v>
+      </c>
+      <c r="D69" s="84">
+        <v>0.6</v>
+      </c>
+      <c r="E69" s="84">
+        <v>0.6</v>
+      </c>
+      <c r="F69" s="84">
+        <f>0.42/3.281</f>
+        <v>0.12800975312404753</v>
+      </c>
+      <c r="G69" s="84">
+        <f t="shared" si="8"/>
+        <v>-4.6083511124657105E-2</v>
+      </c>
       <c r="H69" s="80"/>
       <c r="I69" s="84"/>
-      <c r="J69" s="84">
-        <f>0.13*G67*1350.6</f>
-        <v>1928.4769366577234</v>
-      </c>
+      <c r="J69" s="84"/>
       <c r="K69" s="81"/>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="77"/>
-      <c r="B70" s="92" t="s">
-        <v>30</v>
-      </c>
-      <c r="C70" s="83"/>
-      <c r="D70" s="84"/>
-      <c r="E70" s="84"/>
-      <c r="F70" s="84"/>
-      <c r="G70" s="84"/>
+      <c r="B70" s="94" t="str">
+        <f>B59</f>
+        <v>-for kitchen setup at ward office</v>
+      </c>
+      <c r="C70" s="83">
+        <v>1</v>
+      </c>
+      <c r="D70" s="84">
+        <f>D59</f>
+        <v>1.5</v>
+      </c>
+      <c r="E70" s="84">
+        <f>E59</f>
+        <v>0.68576653459311188</v>
+      </c>
+      <c r="F70" s="84">
+        <v>0.125</v>
+      </c>
+      <c r="G70" s="84">
+        <f t="shared" si="8"/>
+        <v>0.12858122523620846</v>
+      </c>
       <c r="H70" s="80"/>
       <c r="I70" s="84"/>
-      <c r="J70" s="84">
-        <f>0.13*G67*(1912.03+921.59)</f>
-        <v>4046.0319985577216</v>
-      </c>
+      <c r="J70" s="84"/>
       <c r="K70" s="81"/>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="77"/>
-      <c r="B71" s="92" t="s">
-        <v>120</v>
-      </c>
+      <c r="B71" s="94"/>
       <c r="C71" s="83"/>
       <c r="D71" s="84"/>
-      <c r="E71" s="84"/>
+      <c r="E71" s="84" t="s">
+        <v>31</v>
+      </c>
       <c r="F71" s="84"/>
-      <c r="G71" s="84"/>
-      <c r="H71" s="80"/>
-      <c r="I71" s="84"/>
-      <c r="J71" s="84">
-        <f>0.13*G67*392.92</f>
-        <v>561.03743369728477</v>
+      <c r="G71" s="84">
+        <f>SUM(G64:G70)</f>
+        <v>11.112172202794465</v>
+      </c>
+      <c r="H71" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71" s="84">
+        <v>13957.29</v>
+      </c>
+      <c r="J71" s="95">
+        <f>G71*I71</f>
+        <v>155095.80996434117</v>
       </c>
       <c r="K71" s="81"/>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="77"/>
       <c r="B72" s="92" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="C72" s="83"/>
       <c r="D72" s="84"/>
@@ -10960,14 +11001,16 @@
       <c r="H72" s="80"/>
       <c r="I72" s="84"/>
       <c r="J72" s="84">
-        <f>0.13*G67*14.15</f>
-        <v>20.204315603218415</v>
+        <f>0.13*G71*5212.4</f>
+        <v>7529.7412306799624</v>
       </c>
       <c r="K72" s="81"/>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="77"/>
-      <c r="B73" s="92"/>
+      <c r="B73" s="92" t="s">
+        <v>29</v>
+      </c>
       <c r="C73" s="83"/>
       <c r="D73" s="84"/>
       <c r="E73" s="84"/>
@@ -10975,462 +11018,443 @@
       <c r="G73" s="84"/>
       <c r="H73" s="80"/>
       <c r="I73" s="84"/>
-      <c r="J73" s="84"/>
+      <c r="J73" s="84">
+        <f>0.13*G71*1350.6</f>
+        <v>1951.0529710222465</v>
+      </c>
       <c r="K73" s="81"/>
     </row>
-    <row r="74" spans="1:11" ht="30.75">
-      <c r="A74" s="77">
-        <v>9</v>
-      </c>
-      <c r="B74" s="115" t="s">
-        <v>69</v>
+    <row r="74" spans="1:11">
+      <c r="A74" s="77"/>
+      <c r="B74" s="92" t="s">
+        <v>30</v>
       </c>
       <c r="C74" s="83"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="80"/>
+      <c r="D74" s="84"/>
+      <c r="E74" s="84"/>
+      <c r="F74" s="84"/>
       <c r="G74" s="84"/>
       <c r="H74" s="80"/>
       <c r="I74" s="84"/>
-      <c r="J74" s="84"/>
+      <c r="J74" s="84">
+        <f>0.13*G71*(1912.03+921.59)</f>
+        <v>4093.3975416467188</v>
+      </c>
       <c r="K74" s="81"/>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="77"/>
       <c r="B75" s="92" t="s">
-        <v>124</v>
-      </c>
-      <c r="C75" s="83">
-        <v>2</v>
-      </c>
-      <c r="D75" s="80">
-        <f>'Size of water tank'!A3-'Size of water tank'!F3*2</f>
-        <v>4.0130041653967288</v>
-      </c>
-      <c r="E75" s="80"/>
-      <c r="F75" s="80">
-        <f>'Size of water tank'!C3-'Size of water tank'!N3</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G75" s="84">
-        <f>C75*D75*F75</f>
-        <v>11.007935839247352</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C75" s="83"/>
+      <c r="D75" s="84"/>
+      <c r="E75" s="84"/>
+      <c r="F75" s="84"/>
+      <c r="G75" s="84"/>
       <c r="H75" s="80"/>
       <c r="I75" s="84"/>
-      <c r="J75" s="84"/>
+      <c r="J75" s="84">
+        <f>0.13*G71*392.92</f>
+        <v>567.60531124986016</v>
+      </c>
       <c r="K75" s="81"/>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="77"/>
-      <c r="B76" s="96"/>
-      <c r="C76" s="83">
-        <v>2</v>
-      </c>
-      <c r="D76" s="80">
-        <f>'Size of water tank'!B3-'Size of water tank'!F3*2</f>
-        <v>3.8606116021538144</v>
-      </c>
-      <c r="E76" s="80"/>
-      <c r="F76" s="80">
-        <f>'Size of water tank'!C3-'Size of water tank'!N3</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G76" s="84">
-        <f>C76*D76*F76</f>
-        <v>10.589912959275932</v>
-      </c>
+      <c r="B76" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="C76" s="83"/>
+      <c r="D76" s="84"/>
+      <c r="E76" s="84"/>
+      <c r="F76" s="84"/>
+      <c r="G76" s="84"/>
       <c r="H76" s="80"/>
-      <c r="I76" s="97"/>
-      <c r="J76" s="84"/>
+      <c r="I76" s="84"/>
+      <c r="J76" s="84">
+        <f>0.13*G71*14.15</f>
+        <v>20.44084076704042</v>
+      </c>
       <c r="K76" s="81"/>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="77"/>
-      <c r="B77" s="94" t="s">
-        <v>170</v>
-      </c>
-      <c r="C77" s="83">
-        <v>1</v>
-      </c>
-      <c r="D77" s="80">
-        <f>D64*2+D65*2</f>
-        <v>14.528091029157777</v>
-      </c>
-      <c r="E77" s="80"/>
-      <c r="F77" s="80">
-        <f>SQRT(('Size of water tank'!M3)^2+('Size of water tank'!N3)^2)</f>
-        <v>0.43103125948585641</v>
-      </c>
-      <c r="G77" s="84">
-        <f>C77*D77*F77</f>
-        <v>6.2620613742230482</v>
-      </c>
+      <c r="B77" s="92"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="84"/>
+      <c r="E77" s="84"/>
+      <c r="F77" s="84"/>
+      <c r="G77" s="84"/>
       <c r="H77" s="80"/>
-      <c r="I77" s="97"/>
+      <c r="I77" s="84"/>
       <c r="J77" s="84"/>
       <c r="K77" s="81"/>
     </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="77"/>
-      <c r="B78" s="96"/>
+    <row r="78" spans="1:11" ht="30.75">
+      <c r="A78" s="77">
+        <v>9</v>
+      </c>
+      <c r="B78" s="115" t="s">
+        <v>69</v>
+      </c>
       <c r="C78" s="83"/>
-      <c r="D78" s="84"/>
-      <c r="E78" s="84"/>
-      <c r="F78" s="86"/>
-      <c r="G78" s="84">
-        <f>SUM(G75:G76)</f>
-        <v>21.597848798523284</v>
-      </c>
-      <c r="H78" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="I78" s="84">
-        <v>415.5</v>
-      </c>
-      <c r="J78" s="84">
-        <f>G78*I78</f>
-        <v>8973.9061757864238</v>
-      </c>
+      <c r="D78" s="80"/>
+      <c r="E78" s="80"/>
+      <c r="F78" s="80"/>
+      <c r="G78" s="84"/>
+      <c r="H78" s="80"/>
+      <c r="I78" s="84"/>
+      <c r="J78" s="84"/>
       <c r="K78" s="81"/>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="77"/>
       <c r="B79" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" s="83"/>
-      <c r="D79" s="84"/>
-      <c r="E79" s="84"/>
-      <c r="F79" s="86"/>
-      <c r="G79" s="84"/>
+        <v>124</v>
+      </c>
+      <c r="C79" s="83">
+        <v>2</v>
+      </c>
+      <c r="D79" s="80">
+        <f>'Size of water tank'!A3-'Size of water tank'!F3*2</f>
+        <v>4.0130041653967288</v>
+      </c>
+      <c r="E79" s="80"/>
+      <c r="F79" s="80">
+        <f>'Size of water tank'!C3-'Size of water tank'!N3</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G79" s="84">
+        <f>C79*D79*F79</f>
+        <v>11.007935839247352</v>
+      </c>
       <c r="H79" s="80"/>
-      <c r="I79" s="97"/>
-      <c r="J79" s="84">
-        <f>0.13*G78*7010.67/100</f>
-        <v>196.84000782724624</v>
-      </c>
+      <c r="I79" s="84"/>
+      <c r="J79" s="84"/>
       <c r="K79" s="81"/>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="77"/>
-      <c r="B80" s="92" t="s">
-        <v>29</v>
-      </c>
-      <c r="C80" s="83"/>
-      <c r="D80" s="84"/>
-      <c r="E80" s="84"/>
-      <c r="F80" s="86"/>
-      <c r="G80" s="84"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="83">
+        <v>2</v>
+      </c>
+      <c r="D80" s="80">
+        <f>'Size of water tank'!B3-'Size of water tank'!F3*2</f>
+        <v>3.8606116021538144</v>
+      </c>
+      <c r="E80" s="80"/>
+      <c r="F80" s="80">
+        <f>'Size of water tank'!C3-'Size of water tank'!N3</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G80" s="84">
+        <f>C80*D80*F80</f>
+        <v>10.589912959275932</v>
+      </c>
       <c r="H80" s="80"/>
       <c r="I80" s="97"/>
-      <c r="J80" s="84">
-        <f>0.13*G78*4639.73/100</f>
-        <v>130.27064310776416</v>
-      </c>
+      <c r="J80" s="84"/>
       <c r="K80" s="81"/>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="77"/>
-      <c r="B81" s="92"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="84"/>
-      <c r="E81" s="84"/>
-      <c r="F81" s="86"/>
-      <c r="G81" s="84"/>
+      <c r="B81" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="83">
+        <v>1</v>
+      </c>
+      <c r="D81" s="80">
+        <f>D67*2+D68*2</f>
+        <v>14.528091029157777</v>
+      </c>
+      <c r="E81" s="80"/>
+      <c r="F81" s="80">
+        <f>SQRT(('Size of water tank'!M3)^2+('Size of water tank'!N3)^2)</f>
+        <v>0.43103125948585641</v>
+      </c>
+      <c r="G81" s="84">
+        <f>C81*D81*F81</f>
+        <v>6.2620613742230482</v>
+      </c>
       <c r="H81" s="80"/>
       <c r="I81" s="97"/>
       <c r="J81" s="84"/>
       <c r="K81" s="81"/>
     </row>
-    <row r="82" spans="1:11" ht="30.75">
-      <c r="A82" s="77">
-        <v>10</v>
-      </c>
-      <c r="B82" s="115" t="s">
-        <v>68</v>
-      </c>
+    <row r="82" spans="1:11">
+      <c r="A82" s="77"/>
+      <c r="B82" s="96"/>
       <c r="C82" s="83"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="84"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="86"/>
-      <c r="I82" s="84"/>
-      <c r="J82" s="80"/>
+      <c r="D82" s="84"/>
+      <c r="E82" s="84"/>
+      <c r="F82" s="86"/>
+      <c r="G82" s="84">
+        <f>SUM(G79:G80)</f>
+        <v>21.597848798523284</v>
+      </c>
+      <c r="H82" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="84">
+        <v>415.5</v>
+      </c>
+      <c r="J82" s="84">
+        <f>G82*I82</f>
+        <v>8973.9061757864238</v>
+      </c>
       <c r="K82" s="81"/>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="77"/>
       <c r="B83" s="92" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" s="83">
-        <v>1</v>
-      </c>
-      <c r="D83" s="80">
-        <f>'Size of water tank'!A3-'Size of water tank'!F3*2-'Size of water tank'!M3*2</f>
-        <v>3.4034339124250739</v>
-      </c>
-      <c r="E83" s="80">
-        <f>'Size of water tank'!B3-'Size of water tank'!F3*2-'Size of water tank'!M3*2</f>
-        <v>3.2510413491821595</v>
-      </c>
-      <c r="F83" s="84"/>
-      <c r="G83" s="80">
-        <f>E83*D83*C83</f>
-        <v>11.064704378502729</v>
-      </c>
-      <c r="H83" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="84">
-        <v>689.98</v>
-      </c>
-      <c r="J83" s="80">
-        <f>G83*I83</f>
-        <v>7634.424727079313</v>
+        <v>28</v>
+      </c>
+      <c r="C83" s="83"/>
+      <c r="D83" s="84"/>
+      <c r="E83" s="84"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="84"/>
+      <c r="H83" s="80"/>
+      <c r="I83" s="97"/>
+      <c r="J83" s="84">
+        <f>0.13*G82*7010.67/100</f>
+        <v>196.84000782724624</v>
       </c>
       <c r="K83" s="81"/>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="77"/>
       <c r="B84" s="92" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C84" s="83"/>
-      <c r="D84" s="80"/>
-      <c r="E84" s="80"/>
+      <c r="D84" s="84"/>
+      <c r="E84" s="84"/>
       <c r="F84" s="86"/>
-      <c r="G84" s="80"/>
-      <c r="H84" s="86"/>
-      <c r="I84" s="84"/>
-      <c r="J84" s="98">
-        <f>0.13*G83*1694.03/10</f>
-        <v>243.67123505809474</v>
+      <c r="G84" s="84"/>
+      <c r="H84" s="80"/>
+      <c r="I84" s="97"/>
+      <c r="J84" s="84">
+        <f>0.13*G82*4639.73/100</f>
+        <v>130.27064310776416</v>
       </c>
       <c r="K84" s="81"/>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="77"/>
-      <c r="B85" s="92" t="s">
-        <v>29</v>
-      </c>
+      <c r="B85" s="92"/>
       <c r="C85" s="83"/>
-      <c r="D85" s="80"/>
-      <c r="E85" s="80"/>
+      <c r="D85" s="84"/>
+      <c r="E85" s="84"/>
       <c r="F85" s="86"/>
-      <c r="G85" s="80"/>
-      <c r="H85" s="86"/>
-      <c r="I85" s="84"/>
-      <c r="J85" s="98">
-        <f>0.13*G83*572.02/10</f>
-        <v>82.280018581684701</v>
-      </c>
+      <c r="G85" s="84"/>
+      <c r="H85" s="80"/>
+      <c r="I85" s="97"/>
+      <c r="J85" s="84"/>
       <c r="K85" s="81"/>
     </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="77"/>
-      <c r="B86" s="92" t="s">
-        <v>30</v>
+    <row r="86" spans="1:11" ht="30.75">
+      <c r="A86" s="77">
+        <v>10</v>
+      </c>
+      <c r="B86" s="115" t="s">
+        <v>68</v>
       </c>
       <c r="C86" s="83"/>
       <c r="D86" s="80"/>
       <c r="E86" s="80"/>
-      <c r="F86" s="86"/>
+      <c r="F86" s="84"/>
       <c r="G86" s="80"/>
       <c r="H86" s="86"/>
       <c r="I86" s="84"/>
-      <c r="J86" s="98">
-        <f>0.13*G83*1207.6/10</f>
-        <v>173.70258109723864</v>
-      </c>
+      <c r="J86" s="80"/>
       <c r="K86" s="81"/>
     </row>
-    <row r="87" spans="1:11" ht="18" customHeight="1">
+    <row r="87" spans="1:11">
       <c r="A87" s="77"/>
-      <c r="B87" s="92"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="84"/>
-      <c r="E87" s="84"/>
-      <c r="F87" s="86"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="80"/>
-      <c r="I87" s="84"/>
-      <c r="J87" s="84"/>
+      <c r="B87" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C87" s="83">
+        <v>1</v>
+      </c>
+      <c r="D87" s="80">
+        <f>'Size of water tank'!A3-'Size of water tank'!F3*2-'Size of water tank'!M3*2</f>
+        <v>3.4034339124250739</v>
+      </c>
+      <c r="E87" s="80">
+        <f>'Size of water tank'!B3-'Size of water tank'!F3*2-'Size of water tank'!M3*2</f>
+        <v>3.2510413491821595</v>
+      </c>
+      <c r="F87" s="84"/>
+      <c r="G87" s="80">
+        <f>E87*D87*C87</f>
+        <v>11.064704378502729</v>
+      </c>
+      <c r="H87" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="84">
+        <v>689.98</v>
+      </c>
+      <c r="J87" s="80">
+        <f>G87*I87</f>
+        <v>7634.424727079313</v>
+      </c>
       <c r="K87" s="81"/>
     </row>
-    <row r="88" spans="1:11" ht="30.75">
-      <c r="A88" s="77">
-        <v>11</v>
-      </c>
-      <c r="B88" s="115" t="s">
-        <v>70</v>
-      </c>
-      <c r="C88" s="83"/>
+    <row r="88" spans="1:11">
+      <c r="A88" s="77"/>
+      <c r="B88" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="C88" s="83">
+        <v>1</v>
+      </c>
       <c r="D88" s="80"/>
       <c r="E88" s="80"/>
-      <c r="F88" s="80"/>
+      <c r="F88" s="84"/>
       <c r="G88" s="80"/>
-      <c r="H88" s="80"/>
-      <c r="I88" s="80"/>
+      <c r="H88" s="86"/>
+      <c r="I88" s="84"/>
       <c r="J88" s="80"/>
       <c r="K88" s="81"/>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="77"/>
-      <c r="B89" s="92" t="str">
-        <f>B75</f>
-        <v>-At shear wall</v>
-      </c>
-      <c r="C89" s="83">
-        <f>C62</f>
-        <v>2</v>
-      </c>
-      <c r="D89" s="80">
-        <f>D75</f>
-        <v>4.0130041653967288</v>
-      </c>
+      <c r="B89" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="83"/>
+      <c r="D89" s="80"/>
       <c r="E89" s="80"/>
-      <c r="F89" s="80">
-        <f>F75</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G89" s="84">
-        <f>PRODUCT(C89:F89)</f>
-        <v>11.007935839247352</v>
-      </c>
-      <c r="H89" s="80"/>
-      <c r="I89" s="80"/>
-      <c r="J89" s="80"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="80"/>
+      <c r="H89" s="86"/>
+      <c r="I89" s="84"/>
+      <c r="J89" s="98">
+        <f>0.13*G87*1694.03/10</f>
+        <v>243.67123505809474</v>
+      </c>
       <c r="K89" s="81"/>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="77"/>
-      <c r="B90" s="92"/>
-      <c r="C90" s="83">
-        <f>C63</f>
-        <v>2</v>
-      </c>
-      <c r="D90" s="80">
-        <f>D76</f>
-        <v>3.8606116021538144</v>
-      </c>
+      <c r="B90" s="92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" s="83"/>
+      <c r="D90" s="80"/>
       <c r="E90" s="80"/>
-      <c r="F90" s="80">
-        <f>F76</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G90" s="84">
-        <f t="shared" ref="G90:G92" si="8">PRODUCT(C90:F90)</f>
-        <v>10.589912959275932</v>
-      </c>
-      <c r="H90" s="80"/>
-      <c r="I90" s="80"/>
-      <c r="J90" s="80"/>
+      <c r="F90" s="86"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="86"/>
+      <c r="I90" s="84"/>
+      <c r="J90" s="98">
+        <f>0.13*G87*572.02/10</f>
+        <v>82.280018581684701</v>
+      </c>
       <c r="K90" s="81"/>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="77"/>
-      <c r="B91" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="C91" s="83">
-        <v>1</v>
-      </c>
-      <c r="D91" s="80">
-        <f>D77</f>
-        <v>14.528091029157777</v>
-      </c>
+      <c r="B91" s="92" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" s="83"/>
+      <c r="D91" s="80"/>
       <c r="E91" s="80"/>
-      <c r="F91" s="80">
-        <f>F77</f>
-        <v>0.43103125948585641</v>
-      </c>
-      <c r="G91" s="84">
-        <f t="shared" si="8"/>
-        <v>6.2620613742230482</v>
-      </c>
-      <c r="H91" s="80"/>
-      <c r="I91" s="80"/>
-      <c r="J91" s="80"/>
+      <c r="F91" s="86"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="86"/>
+      <c r="I91" s="84"/>
+      <c r="J91" s="98">
+        <f>0.13*G87*1207.6/10</f>
+        <v>173.70258109723864</v>
+      </c>
       <c r="K91" s="81"/>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" ht="18" customHeight="1">
       <c r="A92" s="77"/>
-      <c r="B92" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="C92" s="83">
-        <v>1</v>
-      </c>
-      <c r="D92" s="80">
-        <f>D83</f>
-        <v>3.4034339124250739</v>
-      </c>
-      <c r="E92" s="80">
-        <f>E83</f>
-        <v>3.2510413491821595</v>
-      </c>
-      <c r="F92" s="80"/>
-      <c r="G92" s="84">
-        <f t="shared" si="8"/>
-        <v>11.064704378502729</v>
-      </c>
+      <c r="B92" s="92"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="84"/>
+      <c r="E92" s="84"/>
+      <c r="F92" s="86"/>
+      <c r="G92" s="84"/>
       <c r="H92" s="80"/>
-      <c r="I92" s="80"/>
-      <c r="J92" s="80"/>
+      <c r="I92" s="84"/>
+      <c r="J92" s="84"/>
       <c r="K92" s="81"/>
     </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="77"/>
-      <c r="B93" s="92"/>
+    <row r="93" spans="1:11" ht="30.75">
+      <c r="A93" s="77">
+        <v>11</v>
+      </c>
+      <c r="B93" s="115" t="s">
+        <v>70</v>
+      </c>
       <c r="C93" s="83"/>
       <c r="D93" s="80"/>
       <c r="E93" s="80"/>
       <c r="F93" s="80"/>
-      <c r="G93" s="80">
-        <f>SUM(G89:G92)</f>
-        <v>38.924614551249064</v>
-      </c>
-      <c r="H93" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="80">
-        <v>287.32</v>
-      </c>
-      <c r="J93" s="80">
-        <f>G93*I93</f>
-        <v>11183.820252864882</v>
-      </c>
+      <c r="G93" s="80"/>
+      <c r="H93" s="80"/>
+      <c r="I93" s="80"/>
+      <c r="J93" s="80"/>
       <c r="K93" s="81"/>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="77"/>
-      <c r="B94" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="C94" s="83"/>
-      <c r="D94" s="80"/>
+      <c r="B94" s="92" t="str">
+        <f>B79</f>
+        <v>-At shear wall</v>
+      </c>
+      <c r="C94" s="83">
+        <f>C65</f>
+        <v>2</v>
+      </c>
+      <c r="D94" s="80">
+        <f>D79</f>
+        <v>4.0130041653967288</v>
+      </c>
       <c r="E94" s="80"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="80"/>
+      <c r="F94" s="80">
+        <f>F79</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G94" s="84">
+        <f>PRODUCT(C94:F94)</f>
+        <v>11.007935839247352</v>
+      </c>
       <c r="H94" s="80"/>
       <c r="I94" s="80"/>
-      <c r="J94" s="80">
-        <f>0.13*G93*693.24/10</f>
-        <v>350.79329728960272</v>
-      </c>
+      <c r="J94" s="80"/>
       <c r="K94" s="81"/>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="77"/>
       <c r="B95" s="92"/>
-      <c r="C95" s="83"/>
-      <c r="D95" s="80"/>
+      <c r="C95" s="83">
+        <f>C66</f>
+        <v>2</v>
+      </c>
+      <c r="D95" s="80">
+        <f>D80</f>
+        <v>3.8606116021538144</v>
+      </c>
       <c r="E95" s="80"/>
-      <c r="F95" s="80"/>
-      <c r="G95" s="80"/>
+      <c r="F95" s="80">
+        <f>F80</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G95" s="84">
+        <f t="shared" ref="G95:G97" si="9">PRODUCT(C95:F95)</f>
+        <v>10.589912959275932</v>
+      </c>
       <c r="H95" s="80"/>
       <c r="I95" s="80"/>
       <c r="J95" s="80"/>
@@ -11438,84 +11462,100 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="77"/>
-      <c r="B96" s="92"/>
-      <c r="C96" s="83"/>
-      <c r="D96" s="80"/>
+      <c r="B96" s="94" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" s="83">
+        <v>1</v>
+      </c>
+      <c r="D96" s="80">
+        <f>D81</f>
+        <v>14.528091029157777</v>
+      </c>
       <c r="E96" s="80"/>
-      <c r="F96" s="80"/>
-      <c r="G96" s="80"/>
+      <c r="F96" s="80">
+        <f>F81</f>
+        <v>0.43103125948585641</v>
+      </c>
+      <c r="G96" s="84">
+        <f t="shared" si="9"/>
+        <v>6.2620613742230482</v>
+      </c>
       <c r="H96" s="80"/>
       <c r="I96" s="80"/>
       <c r="J96" s="80"/>
       <c r="K96" s="81"/>
     </row>
-    <row r="97" spans="1:11" ht="33" customHeight="1">
-      <c r="A97" s="77">
-        <v>12</v>
-      </c>
-      <c r="B97" s="96" t="s">
-        <v>73</v>
+    <row r="97" spans="1:11">
+      <c r="A97" s="77"/>
+      <c r="B97" s="94" t="s">
+        <v>125</v>
       </c>
       <c r="C97" s="83">
         <v>1</v>
       </c>
-      <c r="D97" s="84"/>
-      <c r="E97" s="84"/>
-      <c r="F97" s="86"/>
+      <c r="D97" s="80">
+        <f>D87</f>
+        <v>3.4034339124250739</v>
+      </c>
+      <c r="E97" s="80">
+        <f>E87</f>
+        <v>3.2510413491821595</v>
+      </c>
+      <c r="F97" s="80"/>
       <c r="G97" s="84">
-        <f>+C97</f>
-        <v>1</v>
-      </c>
-      <c r="H97" s="80" t="s">
-        <v>33</v>
-      </c>
-      <c r="I97" s="84">
-        <v>4659</v>
-      </c>
-      <c r="J97" s="84">
-        <f>G97*I97</f>
-        <v>4659</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>11.064704378502729</v>
+      </c>
+      <c r="H97" s="80"/>
+      <c r="I97" s="80"/>
+      <c r="J97" s="80"/>
       <c r="K97" s="81"/>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="77"/>
-      <c r="B98" s="85" t="s">
-        <v>74</v>
-      </c>
+      <c r="B98" s="92"/>
       <c r="C98" s="83"/>
-      <c r="D98" s="84"/>
-      <c r="E98" s="84"/>
-      <c r="F98" s="86"/>
-      <c r="G98" s="84"/>
-      <c r="H98" s="80"/>
-      <c r="I98" s="84"/>
-      <c r="J98" s="84">
-        <f>0.13*J97</f>
-        <v>605.67000000000007</v>
+      <c r="D98" s="80"/>
+      <c r="E98" s="80"/>
+      <c r="F98" s="80"/>
+      <c r="G98" s="80">
+        <f>SUM(G94:G97)</f>
+        <v>38.924614551249064</v>
+      </c>
+      <c r="H98" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="80">
+        <v>287.32</v>
+      </c>
+      <c r="J98" s="80">
+        <f>G98*I98</f>
+        <v>11183.820252864882</v>
       </c>
       <c r="K98" s="81"/>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="77"/>
-      <c r="B99" s="96"/>
+      <c r="B99" s="92" t="s">
+        <v>28</v>
+      </c>
       <c r="C99" s="83"/>
-      <c r="D99" s="84"/>
-      <c r="E99" s="84"/>
-      <c r="F99" s="86"/>
-      <c r="G99" s="84"/>
+      <c r="D99" s="80"/>
+      <c r="E99" s="80"/>
+      <c r="F99" s="80"/>
+      <c r="G99" s="80"/>
       <c r="H99" s="80"/>
-      <c r="I99" s="84"/>
-      <c r="J99" s="84"/>
+      <c r="I99" s="80"/>
+      <c r="J99" s="80">
+        <f>0.13*G98*693.24/10</f>
+        <v>350.79329728960272</v>
+      </c>
       <c r="K99" s="81"/>
     </row>
-    <row r="100" spans="1:11" ht="30.75">
-      <c r="A100" s="77">
-        <v>13</v>
-      </c>
-      <c r="B100" s="115" t="s">
-        <v>126</v>
-      </c>
+    <row r="100" spans="1:11">
+      <c r="A100" s="77"/>
+      <c r="B100" s="92"/>
       <c r="C100" s="83"/>
       <c r="D100" s="80"/>
       <c r="E100" s="80"/>
@@ -11528,90 +11568,83 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="77"/>
-      <c r="B101" s="94" t="s">
-        <v>171</v>
-      </c>
-      <c r="C101" s="83">
-        <v>1</v>
-      </c>
-      <c r="D101" s="80">
-        <f>G93</f>
-        <v>38.924614551249064</v>
-      </c>
+      <c r="B101" s="92"/>
+      <c r="C101" s="83"/>
+      <c r="D101" s="80"/>
       <c r="E101" s="80"/>
       <c r="F101" s="80"/>
-      <c r="G101" s="84">
-        <f t="shared" ref="G101" si="9">PRODUCT(C101:F101)</f>
-        <v>38.924614551249064</v>
-      </c>
+      <c r="G101" s="80"/>
       <c r="H101" s="80"/>
       <c r="I101" s="80"/>
       <c r="J101" s="80"/>
       <c r="K101" s="81"/>
     </row>
-    <row r="102" spans="1:11">
-      <c r="A102" s="77"/>
-      <c r="B102" s="92"/>
-      <c r="C102" s="83"/>
-      <c r="D102" s="80"/>
-      <c r="E102" s="80"/>
-      <c r="F102" s="80"/>
-      <c r="G102" s="80">
-        <f>SUM(G101:G101)</f>
-        <v>38.924614551249064</v>
+    <row r="102" spans="1:11" ht="33" customHeight="1">
+      <c r="A102" s="77">
+        <v>12</v>
+      </c>
+      <c r="B102" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="C102" s="83">
+        <v>1</v>
+      </c>
+      <c r="D102" s="84"/>
+      <c r="E102" s="84"/>
+      <c r="F102" s="86"/>
+      <c r="G102" s="84">
+        <f>+C102</f>
+        <v>1</v>
       </c>
       <c r="H102" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="I102" s="80">
-        <v>452.86</v>
-      </c>
-      <c r="J102" s="80">
+        <v>33</v>
+      </c>
+      <c r="I102" s="84">
+        <v>4659</v>
+      </c>
+      <c r="J102" s="84">
         <f>G102*I102</f>
-        <v>17627.400945678652</v>
+        <v>4659</v>
       </c>
       <c r="K102" s="81"/>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="77"/>
-      <c r="B103" s="92" t="s">
-        <v>28</v>
+      <c r="B103" s="85" t="s">
+        <v>74</v>
       </c>
       <c r="C103" s="83"/>
-      <c r="D103" s="80"/>
-      <c r="E103" s="80"/>
-      <c r="F103" s="80"/>
-      <c r="G103" s="80"/>
+      <c r="D103" s="84"/>
+      <c r="E103" s="84"/>
+      <c r="F103" s="86"/>
+      <c r="G103" s="84"/>
       <c r="H103" s="80"/>
-      <c r="I103" s="80"/>
-      <c r="J103" s="80">
-        <f>0.13*G102*1759.18/10</f>
-        <v>890.18024454146234</v>
+      <c r="I103" s="84"/>
+      <c r="J103" s="84">
+        <f>0.13*J102</f>
+        <v>605.67000000000007</v>
       </c>
       <c r="K103" s="81"/>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="77"/>
-      <c r="B104" s="92" t="s">
-        <v>137</v>
-      </c>
+      <c r="B104" s="96"/>
       <c r="C104" s="83"/>
-      <c r="D104" s="80"/>
-      <c r="E104" s="80"/>
-      <c r="F104" s="80"/>
-      <c r="G104" s="80"/>
+      <c r="D104" s="84"/>
+      <c r="E104" s="84"/>
+      <c r="F104" s="86"/>
+      <c r="G104" s="84"/>
       <c r="H104" s="80"/>
-      <c r="I104" s="80"/>
-      <c r="J104" s="80">
-        <f>0.13*G102*572.02/10</f>
-        <v>289.45355420287137</v>
-      </c>
+      <c r="I104" s="84"/>
+      <c r="J104" s="84"/>
       <c r="K104" s="81"/>
     </row>
-    <row r="105" spans="1:11">
-      <c r="A105" s="77"/>
-      <c r="B105" s="92" t="s">
-        <v>138</v>
+    <row r="105" spans="1:11" ht="30.75">
+      <c r="A105" s="77">
+        <v>13</v>
+      </c>
+      <c r="B105" s="115" t="s">
+        <v>126</v>
       </c>
       <c r="C105" s="83"/>
       <c r="D105" s="80"/>
@@ -11620,151 +11653,134 @@
       <c r="G105" s="80"/>
       <c r="H105" s="80"/>
       <c r="I105" s="80"/>
-      <c r="J105" s="80">
-        <f>0.13*G102*515.7/10</f>
-        <v>260.95450841302886</v>
-      </c>
+      <c r="J105" s="80"/>
       <c r="K105" s="81"/>
     </row>
-    <row r="106" spans="1:11" s="171" customFormat="1">
-      <c r="A106" s="166"/>
-      <c r="B106" s="167"/>
-      <c r="C106" s="168"/>
-      <c r="D106" s="169"/>
-      <c r="E106" s="169"/>
-      <c r="F106" s="169"/>
-      <c r="G106" s="169"/>
-      <c r="H106" s="169"/>
-      <c r="I106" s="169"/>
-      <c r="J106" s="169"/>
-      <c r="K106" s="170"/>
-    </row>
-    <row r="107" spans="1:11" ht="30.75">
-      <c r="A107" s="77">
-        <v>14</v>
-      </c>
-      <c r="B107" s="115" t="s">
-        <v>133</v>
-      </c>
+    <row r="106" spans="1:11">
+      <c r="A106" s="77"/>
+      <c r="B106" s="94" t="s">
+        <v>171</v>
+      </c>
+      <c r="C106" s="83">
+        <v>1</v>
+      </c>
+      <c r="D106" s="80">
+        <f>G98</f>
+        <v>38.924614551249064</v>
+      </c>
+      <c r="E106" s="80"/>
+      <c r="F106" s="80"/>
+      <c r="G106" s="84">
+        <f t="shared" ref="G106" si="10">PRODUCT(C106:F106)</f>
+        <v>38.924614551249064</v>
+      </c>
+      <c r="H106" s="80"/>
+      <c r="I106" s="80"/>
+      <c r="J106" s="80"/>
+      <c r="K106" s="81"/>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="77"/>
+      <c r="B107" s="92"/>
       <c r="C107" s="83"/>
       <c r="D107" s="80"/>
       <c r="E107" s="80"/>
       <c r="F107" s="80"/>
-      <c r="G107" s="80"/>
-      <c r="H107" s="80"/>
-      <c r="I107" s="80"/>
-      <c r="J107" s="80"/>
+      <c r="G107" s="80">
+        <f>SUM(G106:G106)</f>
+        <v>38.924614551249064</v>
+      </c>
+      <c r="H107" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="I107" s="80">
+        <v>452.86</v>
+      </c>
+      <c r="J107" s="80">
+        <f>G107*I107</f>
+        <v>17627.400945678652</v>
+      </c>
       <c r="K107" s="81"/>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="77"/>
-      <c r="B108" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="C108" s="83">
-        <v>2</v>
-      </c>
-      <c r="D108" s="80">
-        <v>3.415</v>
-      </c>
+      <c r="B108" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" s="83"/>
+      <c r="D108" s="80"/>
       <c r="E108" s="80"/>
-      <c r="F108" s="80">
-        <v>1.43</v>
-      </c>
-      <c r="G108" s="84">
-        <f>PRODUCT(C108:F108)</f>
-        <v>9.7668999999999997</v>
-      </c>
+      <c r="F108" s="80"/>
+      <c r="G108" s="80"/>
       <c r="H108" s="80"/>
       <c r="I108" s="80"/>
-      <c r="J108" s="80"/>
+      <c r="J108" s="80">
+        <f>0.13*G107*1759.18/10</f>
+        <v>890.18024454146234</v>
+      </c>
       <c r="K108" s="81"/>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="77"/>
-      <c r="B109" s="94"/>
-      <c r="C109" s="83">
-        <v>2</v>
-      </c>
-      <c r="D109" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
-      </c>
+      <c r="B109" s="92" t="s">
+        <v>137</v>
+      </c>
+      <c r="C109" s="83"/>
+      <c r="D109" s="80"/>
       <c r="E109" s="80"/>
-      <c r="F109" s="80">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G109" s="84">
-        <f t="shared" ref="G109:G139" si="10">PRODUCT(C109:F109)</f>
-        <v>4.2240000000000002</v>
-      </c>
+      <c r="F109" s="80"/>
+      <c r="G109" s="80"/>
       <c r="H109" s="80"/>
       <c r="I109" s="80"/>
-      <c r="J109" s="80"/>
+      <c r="J109" s="80">
+        <f>0.13*G107*572.02/10</f>
+        <v>289.45355420287137</v>
+      </c>
       <c r="K109" s="81"/>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="77"/>
-      <c r="B110" s="94"/>
-      <c r="C110" s="83">
-        <v>2</v>
-      </c>
-      <c r="D110" s="80">
-        <v>4</v>
-      </c>
+      <c r="B110" s="92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C110" s="83"/>
+      <c r="D110" s="80"/>
       <c r="E110" s="80"/>
-      <c r="F110" s="80">
-        <v>1.39</v>
-      </c>
-      <c r="G110" s="84">
-        <f t="shared" si="10"/>
-        <v>11.12</v>
-      </c>
+      <c r="F110" s="80"/>
+      <c r="G110" s="80"/>
       <c r="H110" s="80"/>
       <c r="I110" s="80"/>
-      <c r="J110" s="80"/>
+      <c r="J110" s="80">
+        <f>0.13*G107*515.7/10</f>
+        <v>260.95450841302886</v>
+      </c>
       <c r="K110" s="81"/>
     </row>
-    <row r="111" spans="1:11">
-      <c r="A111" s="77"/>
-      <c r="B111" s="94"/>
-      <c r="C111" s="83">
-        <v>2</v>
-      </c>
-      <c r="D111" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
-      </c>
-      <c r="E111" s="80"/>
-      <c r="F111" s="80">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G111" s="84">
-        <f t="shared" si="10"/>
-        <v>4.2240000000000002</v>
-      </c>
-      <c r="H111" s="80"/>
-      <c r="I111" s="80"/>
-      <c r="J111" s="80"/>
-      <c r="K111" s="81"/>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" s="77"/>
-      <c r="B112" s="94"/>
-      <c r="C112" s="83">
-        <v>2</v>
-      </c>
-      <c r="D112" s="80">
-        <v>3.91</v>
-      </c>
+    <row r="111" spans="1:11" s="135" customFormat="1">
+      <c r="A111" s="130"/>
+      <c r="B111" s="131"/>
+      <c r="C111" s="132"/>
+      <c r="D111" s="133"/>
+      <c r="E111" s="133"/>
+      <c r="F111" s="133"/>
+      <c r="G111" s="133"/>
+      <c r="H111" s="133"/>
+      <c r="I111" s="133"/>
+      <c r="J111" s="133"/>
+      <c r="K111" s="134"/>
+    </row>
+    <row r="112" spans="1:11" ht="30.75">
+      <c r="A112" s="77">
+        <v>14</v>
+      </c>
+      <c r="B112" s="115" t="s">
+        <v>133</v>
+      </c>
+      <c r="C112" s="83"/>
+      <c r="D112" s="80"/>
       <c r="E112" s="80"/>
-      <c r="F112" s="80">
-        <v>1.3</v>
-      </c>
-      <c r="G112" s="84">
-        <f t="shared" si="10"/>
-        <v>10.166</v>
-      </c>
+      <c r="F112" s="80"/>
+      <c r="G112" s="80"/>
       <c r="H112" s="80"/>
       <c r="I112" s="80"/>
       <c r="J112" s="80"/>
@@ -11772,21 +11788,22 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="77"/>
-      <c r="B113" s="94"/>
+      <c r="B113" s="94" t="s">
+        <v>134</v>
+      </c>
       <c r="C113" s="83">
         <v>2</v>
       </c>
       <c r="D113" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>3.415</v>
       </c>
       <c r="E113" s="80"/>
       <c r="F113" s="80">
-        <v>2.31</v>
+        <v>1.43</v>
       </c>
       <c r="G113" s="84">
-        <f t="shared" si="10"/>
-        <v>4.4352</v>
+        <f>PRODUCT(C113:F113)</f>
+        <v>9.7668999999999997</v>
       </c>
       <c r="H113" s="80"/>
       <c r="I113" s="80"/>
@@ -11800,15 +11817,16 @@
         <v>2</v>
       </c>
       <c r="D114" s="80">
-        <v>3.96</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E114" s="80"/>
       <c r="F114" s="80">
-        <v>1.37</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G114" s="84">
-        <f t="shared" si="10"/>
-        <v>10.8504</v>
+        <f t="shared" ref="G114:G144" si="11">PRODUCT(C114:F114)</f>
+        <v>4.2240000000000002</v>
       </c>
       <c r="H114" s="80"/>
       <c r="I114" s="80"/>
@@ -11822,16 +11840,15 @@
         <v>2</v>
       </c>
       <c r="D115" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>4</v>
       </c>
       <c r="E115" s="80"/>
       <c r="F115" s="80">
-        <v>2.29</v>
+        <v>1.39</v>
       </c>
       <c r="G115" s="84">
-        <f t="shared" si="10"/>
-        <v>4.3967999999999998</v>
+        <f t="shared" si="11"/>
+        <v>11.12</v>
       </c>
       <c r="H115" s="80"/>
       <c r="I115" s="80"/>
@@ -11845,15 +11862,16 @@
         <v>2</v>
       </c>
       <c r="D116" s="80">
-        <v>3.875</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E116" s="80"/>
       <c r="F116" s="80">
-        <v>1.2649999999999999</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G116" s="84">
-        <f t="shared" si="10"/>
-        <v>9.8037499999999991</v>
+        <f t="shared" si="11"/>
+        <v>4.2240000000000002</v>
       </c>
       <c r="H116" s="80"/>
       <c r="I116" s="80"/>
@@ -11867,16 +11885,15 @@
         <v>2</v>
       </c>
       <c r="D117" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>3.91</v>
       </c>
       <c r="E117" s="80"/>
       <c r="F117" s="80">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="G117" s="84">
-        <f t="shared" si="10"/>
-        <v>4.2047999999999996</v>
+        <f t="shared" si="11"/>
+        <v>10.166</v>
       </c>
       <c r="H117" s="80"/>
       <c r="I117" s="80"/>
@@ -11890,15 +11907,16 @@
         <v>2</v>
       </c>
       <c r="D118" s="80">
-        <v>3.69</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E118" s="80"/>
       <c r="F118" s="80">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="G118" s="84">
-        <f t="shared" si="10"/>
-        <v>9.4464000000000006</v>
+        <f t="shared" si="11"/>
+        <v>4.4352</v>
       </c>
       <c r="H118" s="80"/>
       <c r="I118" s="80"/>
@@ -11912,16 +11930,15 @@
         <v>2</v>
       </c>
       <c r="D119" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>3.96</v>
       </c>
       <c r="E119" s="80"/>
       <c r="F119" s="80">
-        <v>2.19</v>
+        <v>1.37</v>
       </c>
       <c r="G119" s="84">
-        <f t="shared" si="10"/>
-        <v>4.2047999999999996</v>
+        <f t="shared" si="11"/>
+        <v>10.8504</v>
       </c>
       <c r="H119" s="80"/>
       <c r="I119" s="80"/>
@@ -11935,16 +11952,16 @@
         <v>2</v>
       </c>
       <c r="D120" s="80">
-        <f>1.73+2.44</f>
-        <v>4.17</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E120" s="80"/>
       <c r="F120" s="80">
-        <v>1.1200000000000001</v>
+        <v>2.29</v>
       </c>
       <c r="G120" s="84">
-        <f t="shared" si="10"/>
-        <v>9.3408000000000015</v>
+        <f t="shared" si="11"/>
+        <v>4.3967999999999998</v>
       </c>
       <c r="H120" s="80"/>
       <c r="I120" s="80"/>
@@ -11958,16 +11975,15 @@
         <v>2</v>
       </c>
       <c r="D121" s="80">
-        <f>0.34*2</f>
-        <v>0.68</v>
+        <v>3.875</v>
       </c>
       <c r="E121" s="80"/>
       <c r="F121" s="80">
-        <v>2.2599999999999998</v>
+        <v>1.2649999999999999</v>
       </c>
       <c r="G121" s="84">
-        <f t="shared" si="10"/>
-        <v>3.0735999999999999</v>
+        <f t="shared" si="11"/>
+        <v>9.8037499999999991</v>
       </c>
       <c r="H121" s="80"/>
       <c r="I121" s="80"/>
@@ -11981,16 +11997,16 @@
         <v>2</v>
       </c>
       <c r="D122" s="80">
-        <f>0.34*2</f>
-        <v>0.68</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E122" s="80"/>
       <c r="F122" s="80">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="G122" s="84">
-        <f t="shared" si="10"/>
-        <v>2.9239999999999999</v>
+        <f t="shared" si="11"/>
+        <v>4.2047999999999996</v>
       </c>
       <c r="H122" s="80"/>
       <c r="I122" s="80"/>
@@ -12004,15 +12020,15 @@
         <v>2</v>
       </c>
       <c r="D123" s="80">
-        <v>2.5</v>
+        <v>3.69</v>
       </c>
       <c r="E123" s="80"/>
       <c r="F123" s="80">
-        <v>1.1599999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="G123" s="84">
-        <f t="shared" si="10"/>
-        <v>5.8</v>
+        <f t="shared" si="11"/>
+        <v>9.4464000000000006</v>
       </c>
       <c r="H123" s="80"/>
       <c r="I123" s="80"/>
@@ -12031,11 +12047,11 @@
       </c>
       <c r="E124" s="80"/>
       <c r="F124" s="80">
-        <v>2.1800000000000002</v>
+        <v>2.19</v>
       </c>
       <c r="G124" s="84">
-        <f t="shared" si="10"/>
-        <v>4.1856</v>
+        <f t="shared" si="11"/>
+        <v>4.2047999999999996</v>
       </c>
       <c r="H124" s="80"/>
       <c r="I124" s="80"/>
@@ -12049,15 +12065,16 @@
         <v>2</v>
       </c>
       <c r="D125" s="80">
-        <v>3.94</v>
+        <f>1.73+2.44</f>
+        <v>4.17</v>
       </c>
       <c r="E125" s="80"/>
       <c r="F125" s="80">
-        <v>1.2</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G125" s="84">
-        <f t="shared" si="10"/>
-        <v>9.4559999999999995</v>
+        <f t="shared" si="11"/>
+        <v>9.3408000000000015</v>
       </c>
       <c r="H125" s="80"/>
       <c r="I125" s="80"/>
@@ -12071,16 +12088,16 @@
         <v>2</v>
       </c>
       <c r="D126" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <f>0.34*2</f>
+        <v>0.68</v>
       </c>
       <c r="E126" s="80"/>
       <c r="F126" s="80">
-        <v>2.15</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G126" s="84">
-        <f t="shared" si="10"/>
-        <v>4.1280000000000001</v>
+        <f t="shared" si="11"/>
+        <v>3.0735999999999999</v>
       </c>
       <c r="H126" s="80"/>
       <c r="I126" s="80"/>
@@ -12094,15 +12111,16 @@
         <v>2</v>
       </c>
       <c r="D127" s="80">
-        <v>4</v>
+        <f>0.34*2</f>
+        <v>0.68</v>
       </c>
       <c r="E127" s="80"/>
       <c r="F127" s="80">
-        <v>1.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="G127" s="84">
-        <f t="shared" si="10"/>
-        <v>9.1999999999999993</v>
+        <f t="shared" si="11"/>
+        <v>2.9239999999999999</v>
       </c>
       <c r="H127" s="80"/>
       <c r="I127" s="80"/>
@@ -12116,16 +12134,15 @@
         <v>2</v>
       </c>
       <c r="D128" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>2.5</v>
       </c>
       <c r="E128" s="80"/>
       <c r="F128" s="80">
-        <v>2.08</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="G128" s="84">
-        <f t="shared" si="10"/>
-        <v>3.9935999999999998</v>
+        <f t="shared" si="11"/>
+        <v>5.8</v>
       </c>
       <c r="H128" s="80"/>
       <c r="I128" s="80"/>
@@ -12139,15 +12156,16 @@
         <v>2</v>
       </c>
       <c r="D129" s="80">
-        <v>3.97</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E129" s="80"/>
       <c r="F129" s="80">
-        <v>1.25</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="G129" s="84">
-        <f t="shared" si="10"/>
-        <v>9.9250000000000007</v>
+        <f t="shared" si="11"/>
+        <v>4.1856</v>
       </c>
       <c r="H129" s="80"/>
       <c r="I129" s="80"/>
@@ -12161,16 +12179,15 @@
         <v>2</v>
       </c>
       <c r="D130" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>3.94</v>
       </c>
       <c r="E130" s="80"/>
       <c r="F130" s="80">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="G130" s="84">
-        <f t="shared" si="10"/>
-        <v>4.32</v>
+        <f t="shared" si="11"/>
+        <v>9.4559999999999995</v>
       </c>
       <c r="H130" s="80"/>
       <c r="I130" s="80"/>
@@ -12184,15 +12201,16 @@
         <v>2</v>
       </c>
       <c r="D131" s="80">
-        <v>4</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E131" s="80"/>
       <c r="F131" s="80">
-        <v>1.23</v>
+        <v>2.15</v>
       </c>
       <c r="G131" s="84">
-        <f t="shared" si="10"/>
-        <v>9.84</v>
+        <f t="shared" si="11"/>
+        <v>4.1280000000000001</v>
       </c>
       <c r="H131" s="80"/>
       <c r="I131" s="80"/>
@@ -12206,16 +12224,15 @@
         <v>2</v>
       </c>
       <c r="D132" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>4</v>
       </c>
       <c r="E132" s="80"/>
       <c r="F132" s="80">
-        <v>2.25</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G132" s="84">
-        <f t="shared" si="10"/>
-        <v>4.32</v>
+        <f t="shared" si="11"/>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H132" s="80"/>
       <c r="I132" s="80"/>
@@ -12229,15 +12246,16 @@
         <v>2</v>
       </c>
       <c r="D133" s="80">
-        <v>4.0599999999999996</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E133" s="80"/>
       <c r="F133" s="80">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="G133" s="84">
-        <f t="shared" si="10"/>
-        <v>10.718399999999999</v>
+        <f t="shared" si="11"/>
+        <v>3.9935999999999998</v>
       </c>
       <c r="H133" s="80"/>
       <c r="I133" s="80"/>
@@ -12251,16 +12269,15 @@
         <v>2</v>
       </c>
       <c r="D134" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>3.97</v>
       </c>
       <c r="E134" s="80"/>
       <c r="F134" s="80">
-        <v>2.1800000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="G134" s="84">
-        <f t="shared" si="10"/>
-        <v>4.1856</v>
+        <f t="shared" si="11"/>
+        <v>9.9250000000000007</v>
       </c>
       <c r="H134" s="80"/>
       <c r="I134" s="80"/>
@@ -12274,16 +12291,16 @@
         <v>2</v>
       </c>
       <c r="D135" s="80">
-        <f>3.92</f>
-        <v>3.92</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E135" s="80"/>
       <c r="F135" s="80">
-        <v>1.32</v>
+        <v>2.25</v>
       </c>
       <c r="G135" s="84">
-        <f t="shared" si="10"/>
-        <v>10.348800000000001</v>
+        <f t="shared" si="11"/>
+        <v>4.32</v>
       </c>
       <c r="H135" s="80"/>
       <c r="I135" s="80"/>
@@ -12297,16 +12314,15 @@
         <v>2</v>
       </c>
       <c r="D136" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>4</v>
       </c>
       <c r="E136" s="80"/>
       <c r="F136" s="80">
-        <v>2.2799999999999998</v>
+        <v>1.23</v>
       </c>
       <c r="G136" s="84">
-        <f t="shared" si="10"/>
-        <v>4.3775999999999993</v>
+        <f t="shared" si="11"/>
+        <v>9.84</v>
       </c>
       <c r="H136" s="80"/>
       <c r="I136" s="80"/>
@@ -12320,15 +12336,16 @@
         <v>2</v>
       </c>
       <c r="D137" s="80">
-        <v>3.62</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E137" s="80"/>
       <c r="F137" s="80">
-        <v>1.32</v>
+        <v>2.25</v>
       </c>
       <c r="G137" s="84">
-        <f t="shared" si="10"/>
-        <v>9.5568000000000008</v>
+        <f t="shared" si="11"/>
+        <v>4.32</v>
       </c>
       <c r="H137" s="80"/>
       <c r="I137" s="80"/>
@@ -12342,16 +12359,15 @@
         <v>2</v>
       </c>
       <c r="D138" s="80">
-        <f>0.48*2</f>
-        <v>0.96</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="E138" s="80"/>
       <c r="F138" s="80">
-        <v>2.2000000000000002</v>
+        <v>1.32</v>
       </c>
       <c r="G138" s="84">
-        <f t="shared" si="10"/>
-        <v>4.2240000000000002</v>
+        <f t="shared" si="11"/>
+        <v>10.718399999999999</v>
       </c>
       <c r="H138" s="80"/>
       <c r="I138" s="80"/>
@@ -12362,19 +12378,19 @@
       <c r="A139" s="77"/>
       <c r="B139" s="94"/>
       <c r="C139" s="83">
-        <f>-2*16</f>
-        <v>-32</v>
+        <v>2</v>
       </c>
       <c r="D139" s="80">
-        <v>0.23</v>
+        <f>0.48*2</f>
+        <v>0.96</v>
       </c>
       <c r="E139" s="80"/>
       <c r="F139" s="80">
-        <v>1.35</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="G139" s="84">
-        <f t="shared" si="10"/>
-        <v>-9.9360000000000017</v>
+        <f t="shared" si="11"/>
+        <v>4.1856</v>
       </c>
       <c r="H139" s="80"/>
       <c r="I139" s="80"/>
@@ -12383,88 +12399,113 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="77"/>
-      <c r="B140" s="92"/>
-      <c r="C140" s="83"/>
-      <c r="D140" s="80"/>
+      <c r="B140" s="94"/>
+      <c r="C140" s="83">
+        <v>2</v>
+      </c>
+      <c r="D140" s="80">
+        <f>3.92</f>
+        <v>3.92</v>
+      </c>
       <c r="E140" s="80"/>
-      <c r="F140" s="80"/>
-      <c r="G140" s="80">
-        <f>SUM(G108:G139)</f>
-        <v>200.82485</v>
-      </c>
-      <c r="H140" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="I140" s="80">
-        <v>253.8</v>
-      </c>
-      <c r="J140" s="80">
-        <f>G140*I140</f>
-        <v>50969.34693</v>
-      </c>
+      <c r="F140" s="80">
+        <v>1.32</v>
+      </c>
+      <c r="G140" s="84">
+        <f t="shared" si="11"/>
+        <v>10.348800000000001</v>
+      </c>
+      <c r="H140" s="80"/>
+      <c r="I140" s="80"/>
+      <c r="J140" s="80"/>
       <c r="K140" s="81"/>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="77"/>
-      <c r="B141" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="C141" s="83"/>
-      <c r="D141" s="80"/>
+      <c r="B141" s="94"/>
+      <c r="C141" s="83">
+        <v>2</v>
+      </c>
+      <c r="D141" s="80">
+        <f>0.48*2</f>
+        <v>0.96</v>
+      </c>
       <c r="E141" s="80"/>
-      <c r="F141" s="80"/>
-      <c r="G141" s="80"/>
+      <c r="F141" s="80">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="G141" s="84">
+        <f t="shared" si="11"/>
+        <v>4.3775999999999993</v>
+      </c>
       <c r="H141" s="80"/>
       <c r="I141" s="80"/>
-      <c r="J141" s="80">
-        <f>0.13*G140*2304/100</f>
-        <v>601.51059071999998</v>
-      </c>
+      <c r="J141" s="80"/>
       <c r="K141" s="81"/>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="77"/>
-      <c r="B142" s="92" t="s">
-        <v>136</v>
-      </c>
-      <c r="C142" s="83"/>
-      <c r="D142" s="80"/>
+      <c r="B142" s="94"/>
+      <c r="C142" s="83">
+        <v>2</v>
+      </c>
+      <c r="D142" s="80">
+        <v>3.62</v>
+      </c>
       <c r="E142" s="80"/>
-      <c r="F142" s="80"/>
-      <c r="G142" s="80"/>
+      <c r="F142" s="80">
+        <v>1.32</v>
+      </c>
+      <c r="G142" s="84">
+        <f t="shared" si="11"/>
+        <v>9.5568000000000008</v>
+      </c>
       <c r="H142" s="80"/>
       <c r="I142" s="80"/>
-      <c r="J142" s="80">
-        <f>0.13*G140*10432/100</f>
-        <v>2723.5062857600001</v>
-      </c>
+      <c r="J142" s="80"/>
       <c r="K142" s="81"/>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="77"/>
-      <c r="B143" s="92"/>
-      <c r="C143" s="83"/>
-      <c r="D143" s="80"/>
+      <c r="B143" s="94"/>
+      <c r="C143" s="83">
+        <v>2</v>
+      </c>
+      <c r="D143" s="80">
+        <f>0.48*2</f>
+        <v>0.96</v>
+      </c>
       <c r="E143" s="80"/>
-      <c r="F143" s="80"/>
-      <c r="G143" s="80"/>
+      <c r="F143" s="80">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G143" s="84">
+        <f t="shared" si="11"/>
+        <v>4.2240000000000002</v>
+      </c>
       <c r="H143" s="80"/>
       <c r="I143" s="80"/>
       <c r="J143" s="80"/>
       <c r="K143" s="81"/>
     </row>
-    <row r="144" spans="1:11" ht="31.5">
-      <c r="A144" s="77">
-        <v>15</v>
-      </c>
-      <c r="B144" s="120" t="s">
-        <v>141</v>
-      </c>
-      <c r="C144" s="83"/>
-      <c r="D144" s="80"/>
+    <row r="144" spans="1:11">
+      <c r="A144" s="77"/>
+      <c r="B144" s="94"/>
+      <c r="C144" s="83">
+        <f>-2*16</f>
+        <v>-32</v>
+      </c>
+      <c r="D144" s="80">
+        <v>0.23</v>
+      </c>
       <c r="E144" s="80"/>
-      <c r="F144" s="80"/>
-      <c r="G144" s="80"/>
+      <c r="F144" s="80">
+        <v>1.35</v>
+      </c>
+      <c r="G144" s="84">
+        <f t="shared" si="11"/>
+        <v>-9.9360000000000017</v>
+      </c>
       <c r="H144" s="80"/>
       <c r="I144" s="80"/>
       <c r="J144" s="80"/>
@@ -12472,70 +12513,61 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="77"/>
-      <c r="B145" s="94" t="s">
-        <v>142</v>
-      </c>
-      <c r="C145" s="83">
-        <v>1</v>
-      </c>
-      <c r="D145" s="80">
-        <f>0.9</f>
-        <v>0.9</v>
-      </c>
+      <c r="B145" s="92"/>
+      <c r="C145" s="83"/>
+      <c r="D145" s="80"/>
       <c r="E145" s="80"/>
       <c r="F145" s="80"/>
-      <c r="G145" s="84">
-        <f t="shared" ref="G145:G147" si="11">PRODUCT(C145:F145)</f>
-        <v>0.9</v>
-      </c>
-      <c r="H145" s="80"/>
-      <c r="I145" s="80"/>
-      <c r="J145" s="80"/>
+      <c r="G145" s="80">
+        <f>SUM(G113:G144)</f>
+        <v>200.82485</v>
+      </c>
+      <c r="H145" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="I145" s="80">
+        <v>253.8</v>
+      </c>
+      <c r="J145" s="80">
+        <f>G145*I145</f>
+        <v>50969.34693</v>
+      </c>
       <c r="K145" s="81"/>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="77"/>
-      <c r="B146" s="94" t="s">
-        <v>143</v>
-      </c>
-      <c r="C146" s="83">
-        <v>1</v>
-      </c>
-      <c r="D146" s="80">
-        <f>1.5</f>
-        <v>1.5</v>
-      </c>
+      <c r="B146" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="C146" s="83"/>
+      <c r="D146" s="80"/>
       <c r="E146" s="80"/>
       <c r="F146" s="80"/>
-      <c r="G146" s="84">
-        <f t="shared" si="11"/>
-        <v>1.5</v>
-      </c>
+      <c r="G146" s="80"/>
       <c r="H146" s="80"/>
       <c r="I146" s="80"/>
-      <c r="J146" s="80"/>
+      <c r="J146" s="80">
+        <f>0.13*G145*2304/100</f>
+        <v>601.51059071999998</v>
+      </c>
       <c r="K146" s="81"/>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="77"/>
-      <c r="B147" s="94" t="s">
-        <v>144</v>
-      </c>
-      <c r="C147" s="83">
-        <v>2</v>
-      </c>
-      <c r="D147" s="80">
-        <v>0.9</v>
-      </c>
+      <c r="B147" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="C147" s="83"/>
+      <c r="D147" s="80"/>
       <c r="E147" s="80"/>
       <c r="F147" s="80"/>
-      <c r="G147" s="84">
-        <f t="shared" si="11"/>
-        <v>1.8</v>
-      </c>
+      <c r="G147" s="80"/>
       <c r="H147" s="80"/>
       <c r="I147" s="80"/>
-      <c r="J147" s="80"/>
+      <c r="J147" s="80">
+        <f>0.13*G145*10432/100</f>
+        <v>2723.5062857600001</v>
+      </c>
       <c r="K147" s="81"/>
     </row>
     <row r="148" spans="1:11">
@@ -12545,26 +12577,18 @@
       <c r="D148" s="80"/>
       <c r="E148" s="80"/>
       <c r="F148" s="80"/>
-      <c r="G148" s="80">
-        <f>SUM(G145:G147)</f>
-        <v>4.2</v>
-      </c>
-      <c r="H148" s="80" t="s">
-        <v>145</v>
-      </c>
-      <c r="I148" s="80">
-        <v>248</v>
-      </c>
-      <c r="J148" s="80">
-        <f>G148*I148</f>
-        <v>1041.6000000000001</v>
-      </c>
+      <c r="G148" s="80"/>
+      <c r="H148" s="80"/>
+      <c r="I148" s="80"/>
+      <c r="J148" s="80"/>
       <c r="K148" s="81"/>
     </row>
-    <row r="149" spans="1:11">
-      <c r="A149" s="77"/>
-      <c r="B149" s="94" t="s">
-        <v>146</v>
+    <row r="149" spans="1:11" ht="31.5">
+      <c r="A149" s="77">
+        <v>15</v>
+      </c>
+      <c r="B149" s="120" t="s">
+        <v>141</v>
       </c>
       <c r="C149" s="83"/>
       <c r="D149" s="80"/>
@@ -12573,37 +12597,50 @@
       <c r="G149" s="80"/>
       <c r="H149" s="80"/>
       <c r="I149" s="80"/>
-      <c r="J149" s="80">
-        <f>0.13*J148</f>
-        <v>135.40800000000002</v>
-      </c>
+      <c r="J149" s="80"/>
       <c r="K149" s="81"/>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="77"/>
-      <c r="B150" s="92"/>
-      <c r="C150" s="83"/>
-      <c r="D150" s="80"/>
+      <c r="B150" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="C150" s="83">
+        <v>1</v>
+      </c>
+      <c r="D150" s="80">
+        <f>0.9</f>
+        <v>0.9</v>
+      </c>
       <c r="E150" s="80"/>
       <c r="F150" s="80"/>
-      <c r="G150" s="80"/>
+      <c r="G150" s="84">
+        <f t="shared" ref="G150:G152" si="12">PRODUCT(C150:F150)</f>
+        <v>0.9</v>
+      </c>
       <c r="H150" s="80"/>
       <c r="I150" s="80"/>
       <c r="J150" s="80"/>
       <c r="K150" s="81"/>
     </row>
-    <row r="151" spans="1:11" ht="31.5">
-      <c r="A151" s="77">
-        <v>16</v>
-      </c>
-      <c r="B151" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="C151" s="83"/>
-      <c r="D151" s="80"/>
+    <row r="151" spans="1:11">
+      <c r="A151" s="77"/>
+      <c r="B151" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="C151" s="83">
+        <v>1</v>
+      </c>
+      <c r="D151" s="80">
+        <f>1.5</f>
+        <v>1.5</v>
+      </c>
       <c r="E151" s="80"/>
       <c r="F151" s="80"/>
-      <c r="G151" s="80"/>
+      <c r="G151" s="84">
+        <f t="shared" si="12"/>
+        <v>1.5</v>
+      </c>
       <c r="H151" s="80"/>
       <c r="I151" s="80"/>
       <c r="J151" s="80"/>
@@ -12612,19 +12649,19 @@
     <row r="152" spans="1:11">
       <c r="A152" s="77"/>
       <c r="B152" s="94" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C152" s="83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="80">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="E152" s="80"/>
       <c r="F152" s="80"/>
       <c r="G152" s="84">
-        <f t="shared" ref="G152" si="12">PRODUCT(C152:F152)</f>
-        <v>9</v>
+        <f t="shared" si="12"/>
+        <v>1.8</v>
       </c>
       <c r="H152" s="80"/>
       <c r="I152" s="80"/>
@@ -12639,18 +12676,18 @@
       <c r="E153" s="80"/>
       <c r="F153" s="80"/>
       <c r="G153" s="80">
-        <f>SUM(G152:G152)</f>
-        <v>9</v>
+        <f>SUM(G150:G152)</f>
+        <v>4.2</v>
       </c>
       <c r="H153" s="80" t="s">
         <v>145</v>
       </c>
       <c r="I153" s="80">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="J153" s="80">
         <f>G153*I153</f>
-        <v>675</v>
+        <v>1041.6000000000001</v>
       </c>
       <c r="K153" s="81"/>
     </row>
@@ -12668,7 +12705,7 @@
       <c r="I154" s="80"/>
       <c r="J154" s="80">
         <f>0.13*J153</f>
-        <v>87.75</v>
+        <v>135.40800000000002</v>
       </c>
       <c r="K154" s="81"/>
     </row>
@@ -12685,12 +12722,12 @@
       <c r="J155" s="80"/>
       <c r="K155" s="81"/>
     </row>
-    <row r="156" spans="1:11" ht="47.25">
+    <row r="156" spans="1:11" ht="31.5">
       <c r="A156" s="77">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B156" s="120" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C156" s="83"/>
       <c r="D156" s="80"/>
@@ -12710,12 +12747,14 @@
       <c r="C157" s="83">
         <v>1</v>
       </c>
-      <c r="D157" s="80"/>
+      <c r="D157" s="80">
+        <v>9</v>
+      </c>
       <c r="E157" s="80"/>
       <c r="F157" s="80"/>
       <c r="G157" s="84">
         <f t="shared" ref="G157" si="13">PRODUCT(C157:F157)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H157" s="80"/>
       <c r="I157" s="80"/>
@@ -12731,17 +12770,17 @@
       <c r="F158" s="80"/>
       <c r="G158" s="80">
         <f>SUM(G157:G157)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H158" s="80" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I158" s="80">
-        <v>1070</v>
+        <v>75</v>
       </c>
       <c r="J158" s="80">
         <f>G158*I158</f>
-        <v>1070</v>
+        <v>675</v>
       </c>
       <c r="K158" s="81"/>
     </row>
@@ -12759,7 +12798,7 @@
       <c r="I159" s="80"/>
       <c r="J159" s="80">
         <f>0.13*J158</f>
-        <v>139.1</v>
+        <v>87.75</v>
       </c>
       <c r="K159" s="81"/>
     </row>
@@ -12776,12 +12815,12 @@
       <c r="J160" s="80"/>
       <c r="K160" s="81"/>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" ht="47.25">
       <c r="A161" s="77">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B161" s="120" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C161" s="83"/>
       <c r="D161" s="80"/>
@@ -12796,17 +12835,17 @@
     <row r="162" spans="1:11">
       <c r="A162" s="77"/>
       <c r="B162" s="94" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C162" s="83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" s="80"/>
       <c r="E162" s="80"/>
       <c r="F162" s="80"/>
       <c r="G162" s="84">
         <f t="shared" ref="G162" si="14">PRODUCT(C162:F162)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H162" s="80"/>
       <c r="I162" s="80"/>
@@ -12822,17 +12861,17 @@
       <c r="F163" s="80"/>
       <c r="G163" s="80">
         <f>SUM(G162:G162)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H163" s="80" t="s">
         <v>149</v>
       </c>
       <c r="I163" s="80">
-        <v>750</v>
+        <v>1070</v>
       </c>
       <c r="J163" s="80">
         <f>G163*I163</f>
-        <v>1500</v>
+        <v>1070</v>
       </c>
       <c r="K163" s="81"/>
     </row>
@@ -12850,7 +12889,7 @@
       <c r="I164" s="80"/>
       <c r="J164" s="80">
         <f>0.13*J163</f>
-        <v>195</v>
+        <v>139.1</v>
       </c>
       <c r="K164" s="81"/>
     </row>
@@ -12867,217 +12906,209 @@
       <c r="J165" s="80"/>
       <c r="K165" s="81"/>
     </row>
-    <row r="166" spans="1:11" ht="33" customHeight="1">
+    <row r="166" spans="1:11">
       <c r="A166" s="77">
-        <v>19</v>
-      </c>
-      <c r="B166" s="93" t="s">
-        <v>127</v>
-      </c>
-      <c r="C166" s="83">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B166" s="120" t="s">
+        <v>151</v>
+      </c>
+      <c r="C166" s="83"/>
       <c r="D166" s="80"/>
       <c r="E166" s="80"/>
       <c r="F166" s="80"/>
-      <c r="G166" s="80">
-        <v>1</v>
-      </c>
-      <c r="H166" s="80" t="s">
-        <v>128</v>
-      </c>
-      <c r="I166" s="84">
-        <v>15000</v>
-      </c>
-      <c r="J166" s="84">
-        <f>G166*I166</f>
-        <v>15000</v>
-      </c>
+      <c r="G166" s="80"/>
+      <c r="H166" s="80"/>
+      <c r="I166" s="80"/>
+      <c r="J166" s="80"/>
       <c r="K166" s="81"/>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="77"/>
-      <c r="B167" s="99"/>
-      <c r="C167" s="83"/>
+      <c r="B167" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="C167" s="83">
+        <v>2</v>
+      </c>
       <c r="D167" s="80"/>
       <c r="E167" s="80"/>
-      <c r="F167" s="84"/>
-      <c r="G167" s="80"/>
+      <c r="F167" s="80"/>
+      <c r="G167" s="84">
+        <f t="shared" ref="G167" si="15">PRODUCT(C167:F167)</f>
+        <v>2</v>
+      </c>
       <c r="H167" s="80"/>
-      <c r="I167" s="84"/>
-      <c r="J167" s="84"/>
+      <c r="I167" s="80"/>
+      <c r="J167" s="80"/>
       <c r="K167" s="81"/>
     </row>
-    <row r="168" spans="1:11" ht="33" customHeight="1">
-      <c r="A168" s="77">
-        <v>20</v>
-      </c>
-      <c r="B168" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="C168" s="83">
-        <v>1</v>
-      </c>
+    <row r="168" spans="1:11">
+      <c r="A168" s="77"/>
+      <c r="B168" s="92"/>
+      <c r="C168" s="83"/>
       <c r="D168" s="80"/>
       <c r="E168" s="80"/>
       <c r="F168" s="80"/>
       <c r="G168" s="80">
+        <f>SUM(G167:G167)</f>
+        <v>2</v>
+      </c>
+      <c r="H168" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="I168" s="80">
+        <v>750</v>
+      </c>
+      <c r="J168" s="80">
+        <f>G168*I168</f>
+        <v>1500</v>
+      </c>
+      <c r="K168" s="81"/>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" s="77"/>
+      <c r="B169" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="C169" s="83"/>
+      <c r="D169" s="80"/>
+      <c r="E169" s="80"/>
+      <c r="F169" s="80"/>
+      <c r="G169" s="80"/>
+      <c r="H169" s="80"/>
+      <c r="I169" s="80"/>
+      <c r="J169" s="80">
+        <f>0.13*J168</f>
+        <v>195</v>
+      </c>
+      <c r="K169" s="81"/>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" s="77"/>
+      <c r="B170" s="92"/>
+      <c r="C170" s="83"/>
+      <c r="D170" s="80"/>
+      <c r="E170" s="80"/>
+      <c r="F170" s="80"/>
+      <c r="G170" s="80"/>
+      <c r="H170" s="80"/>
+      <c r="I170" s="80"/>
+      <c r="J170" s="80"/>
+      <c r="K170" s="81"/>
+    </row>
+    <row r="171" spans="1:11" ht="33" customHeight="1">
+      <c r="A171" s="77">
+        <v>19</v>
+      </c>
+      <c r="B171" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="C171" s="83">
         <v>1</v>
       </c>
-      <c r="H168" s="80" t="s">
+      <c r="D171" s="80"/>
+      <c r="E171" s="80"/>
+      <c r="F171" s="80"/>
+      <c r="G171" s="80">
+        <v>1</v>
+      </c>
+      <c r="H171" s="80" t="s">
+        <v>128</v>
+      </c>
+      <c r="I171" s="84">
+        <v>15000</v>
+      </c>
+      <c r="J171" s="84">
+        <f>G171*I171</f>
+        <v>15000</v>
+      </c>
+      <c r="K171" s="81"/>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" s="77"/>
+      <c r="B172" s="99"/>
+      <c r="C172" s="83"/>
+      <c r="D172" s="80"/>
+      <c r="E172" s="80"/>
+      <c r="F172" s="84"/>
+      <c r="G172" s="80"/>
+      <c r="H172" s="80"/>
+      <c r="I172" s="84"/>
+      <c r="J172" s="84"/>
+      <c r="K172" s="81"/>
+    </row>
+    <row r="173" spans="1:11" ht="33" customHeight="1">
+      <c r="A173" s="77">
+        <v>20</v>
+      </c>
+      <c r="B173" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="C173" s="83">
+        <v>1</v>
+      </c>
+      <c r="D173" s="80"/>
+      <c r="E173" s="80"/>
+      <c r="F173" s="80"/>
+      <c r="G173" s="80">
+        <v>1</v>
+      </c>
+      <c r="H173" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="I168" s="84">
+      <c r="I173" s="84">
         <v>500</v>
       </c>
-      <c r="J168" s="84">
-        <f>G168*I168</f>
+      <c r="J173" s="84">
+        <f>G173*I173</f>
         <v>500</v>
       </c>
-      <c r="K168" s="81"/>
-    </row>
-    <row r="169" spans="1:11">
-      <c r="A169" s="100"/>
-      <c r="B169" s="101"/>
-      <c r="C169" s="80"/>
-      <c r="D169" s="84"/>
-      <c r="E169" s="84"/>
-      <c r="F169" s="84"/>
-      <c r="G169" s="84"/>
-      <c r="H169" s="80"/>
-      <c r="I169" s="84"/>
-      <c r="J169" s="102">
-        <f>SUM(J12:J168)</f>
-        <v>592843.42565216997</v>
-      </c>
-      <c r="K169" s="103"/>
-    </row>
-    <row r="170" spans="1:11">
-      <c r="A170" s="104"/>
-      <c r="B170" s="105"/>
-      <c r="C170" s="65"/>
-      <c r="D170" s="65"/>
-      <c r="E170" s="65"/>
-      <c r="F170" s="65"/>
-      <c r="G170" s="65"/>
-      <c r="H170" s="65"/>
-      <c r="I170" s="65"/>
-      <c r="J170" s="106"/>
-      <c r="K170" s="107"/>
-    </row>
-    <row r="171" spans="1:11">
-      <c r="A171" s="104"/>
-      <c r="B171" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="C171" s="130" t="s">
-        <v>66</v>
-      </c>
-      <c r="D171" s="130"/>
-      <c r="E171" s="75" t="s">
-        <v>67</v>
-      </c>
-      <c r="F171" s="108"/>
-      <c r="G171" s="109"/>
-      <c r="H171" s="108"/>
-      <c r="I171" s="109"/>
-      <c r="J171" s="108"/>
-      <c r="K171" s="108"/>
-    </row>
-    <row r="172" spans="1:11">
-      <c r="A172" s="104"/>
-      <c r="B172" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="C172" s="128">
-        <f>+J169</f>
-        <v>592843.42565216997</v>
-      </c>
-      <c r="D172" s="128"/>
-      <c r="E172" s="110"/>
-      <c r="F172" s="108"/>
-      <c r="G172" s="111"/>
-      <c r="H172" s="108"/>
-      <c r="I172" s="109"/>
-      <c r="J172" s="108"/>
-      <c r="K172" s="108"/>
-    </row>
-    <row r="173" spans="1:11">
-      <c r="A173" s="104"/>
-      <c r="B173" s="79" t="s">
-        <v>14</v>
-      </c>
-      <c r="C173" s="128">
-        <v>480000</v>
-      </c>
-      <c r="D173" s="128"/>
-      <c r="E173" s="112">
-        <v>100</v>
-      </c>
-      <c r="F173" s="108"/>
-      <c r="G173" s="111"/>
-      <c r="H173" s="108"/>
-      <c r="I173" s="109"/>
-      <c r="J173" s="108"/>
-      <c r="K173" s="108"/>
+      <c r="K173" s="81"/>
     </row>
     <row r="174" spans="1:11">
-      <c r="A174" s="104"/>
-      <c r="B174" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="C174" s="128">
-        <f>0.95*C173</f>
-        <v>456000</v>
-      </c>
-      <c r="D174" s="128"/>
-      <c r="E174" s="113">
-        <f>C174/C172*100</f>
-        <v>76.917442324399161</v>
-      </c>
-      <c r="F174" s="108"/>
-      <c r="G174" s="111"/>
-      <c r="H174" s="108"/>
-      <c r="I174" s="109"/>
-      <c r="J174" s="108"/>
-      <c r="K174" s="108"/>
+      <c r="A174" s="100"/>
+      <c r="B174" s="101"/>
+      <c r="C174" s="80"/>
+      <c r="D174" s="84"/>
+      <c r="E174" s="84"/>
+      <c r="F174" s="84"/>
+      <c r="G174" s="84"/>
+      <c r="H174" s="80"/>
+      <c r="I174" s="84"/>
+      <c r="J174" s="102">
+        <f>SUM(J12:J173)</f>
+        <v>597573.34594592568</v>
+      </c>
+      <c r="K174" s="103"/>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="104"/>
-      <c r="B175" s="79" t="s">
-        <v>15</v>
-      </c>
-      <c r="C175" s="128">
-        <f>C172-C174</f>
-        <v>136843.42565216997</v>
-      </c>
-      <c r="D175" s="128"/>
-      <c r="E175" s="113">
-        <f>C175/C173*100</f>
-        <v>28.509047010868745</v>
-      </c>
-      <c r="F175" s="108"/>
-      <c r="G175" s="111"/>
-      <c r="H175" s="108"/>
-      <c r="I175" s="109"/>
-      <c r="J175" s="108"/>
-      <c r="K175" s="108"/>
+      <c r="B175" s="105"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="65"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="65"/>
+      <c r="H175" s="65"/>
+      <c r="I175" s="65"/>
+      <c r="J175" s="106"/>
+      <c r="K175" s="107"/>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="104"/>
-      <c r="B176" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C176" s="128">
-        <f>E176*C173/100</f>
-        <v>9600</v>
-      </c>
-      <c r="D176" s="128"/>
-      <c r="E176" s="113">
-        <v>2</v>
+      <c r="B176" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C176" s="137" t="s">
+        <v>66</v>
+      </c>
+      <c r="D176" s="137"/>
+      <c r="E176" s="75" t="s">
+        <v>67</v>
       </c>
       <c r="F176" s="108"/>
-      <c r="G176" s="111"/>
+      <c r="G176" s="109"/>
       <c r="H176" s="108"/>
       <c r="I176" s="109"/>
       <c r="J176" s="108"/>
@@ -13086,42 +13117,141 @@
     <row r="177" spans="1:11">
       <c r="A177" s="104"/>
       <c r="B177" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="C177" s="129">
-        <f>E177*C173/100</f>
-        <v>14400</v>
-      </c>
-      <c r="D177" s="129"/>
-      <c r="E177" s="113">
-        <v>3</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C177" s="138">
+        <f>+J174</f>
+        <v>597573.34594592568</v>
+      </c>
+      <c r="D177" s="138"/>
+      <c r="E177" s="110"/>
       <c r="F177" s="108"/>
-      <c r="G177" s="114"/>
+      <c r="G177" s="111"/>
       <c r="H177" s="108"/>
       <c r="I177" s="109"/>
       <c r="J177" s="108"/>
       <c r="K177" s="108"/>
     </row>
     <row r="178" spans="1:11">
-      <c r="F178" s="37"/>
+      <c r="A178" s="104"/>
+      <c r="B178" s="79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" s="138">
+        <v>480000</v>
+      </c>
+      <c r="D178" s="138"/>
+      <c r="E178" s="112">
+        <v>100</v>
+      </c>
+      <c r="F178" s="108"/>
+      <c r="G178" s="111"/>
+      <c r="H178" s="108"/>
+      <c r="I178" s="109"/>
+      <c r="J178" s="108"/>
+      <c r="K178" s="108"/>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" s="104"/>
+      <c r="B179" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179" s="138">
+        <f>0.95*C178</f>
+        <v>456000</v>
+      </c>
+      <c r="D179" s="138"/>
+      <c r="E179" s="113">
+        <f>C179/C177*100</f>
+        <v>76.308624387886155</v>
+      </c>
+      <c r="F179" s="108"/>
+      <c r="G179" s="111"/>
+      <c r="H179" s="108"/>
+      <c r="I179" s="109"/>
+      <c r="J179" s="108"/>
+      <c r="K179" s="108"/>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" s="104"/>
+      <c r="B180" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="138">
+        <f>C177-C179</f>
+        <v>141573.34594592568</v>
+      </c>
+      <c r="D180" s="138"/>
+      <c r="E180" s="113">
+        <f>C180/C178*100</f>
+        <v>29.494447072067853</v>
+      </c>
+      <c r="F180" s="108"/>
+      <c r="G180" s="111"/>
+      <c r="H180" s="108"/>
+      <c r="I180" s="109"/>
+      <c r="J180" s="108"/>
+      <c r="K180" s="108"/>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" s="104"/>
+      <c r="B181" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" s="138">
+        <f>E181*C178/100</f>
+        <v>9600</v>
+      </c>
+      <c r="D181" s="138"/>
+      <c r="E181" s="113">
+        <v>2</v>
+      </c>
+      <c r="F181" s="108"/>
+      <c r="G181" s="111"/>
+      <c r="H181" s="108"/>
+      <c r="I181" s="109"/>
+      <c r="J181" s="108"/>
+      <c r="K181" s="108"/>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182" s="104"/>
+      <c r="B182" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C182" s="136">
+        <f>E182*C178/100</f>
+        <v>14400</v>
+      </c>
+      <c r="D182" s="136"/>
+      <c r="E182" s="113">
+        <v>3</v>
+      </c>
+      <c r="F182" s="108"/>
+      <c r="G182" s="114"/>
+      <c r="H182" s="108"/>
+      <c r="I182" s="109"/>
+      <c r="J182" s="108"/>
+      <c r="K182" s="108"/>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="F183" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="C179:D179"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C181:D181"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>
